--- a/ERT_CHEM_DB.xlsx
+++ b/ERT_CHEM_DB.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AR85"/>
+  <dimension ref="A1:AR81"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -619,10 +619,10 @@
         <v>OSHA</v>
       </c>
       <c r="N2" t="str">
-        <v>3 ppm</v>
+        <v>1 ppm</v>
       </c>
       <c r="O2" t="str">
-        <v>ACGIH</v>
+        <v>OSHA</v>
       </c>
       <c r="P2" t="str">
         <v>6 ppm</v>
@@ -747,16 +747,16 @@
         <v>농황산: 강산성 (물 접촉 시 강한 발열)</v>
       </c>
       <c r="L3" t="str">
-        <v>0.2 mg/m³</v>
+        <v>1 mg/m³</v>
       </c>
       <c r="M3" t="str">
         <v>KOSHA</v>
       </c>
       <c r="N3" t="str">
-        <v>0.6 mg/m³</v>
+        <v>3 mg/m³</v>
       </c>
       <c r="O3" t="str">
-        <v>ACGIH</v>
+        <v>대표 참고값</v>
       </c>
       <c r="P3" t="str">
         <v>설정 없음</v>
@@ -2367,10 +2367,10 @@
         <v>제조사 SDS</v>
       </c>
       <c r="P15" t="str">
-        <v>제품 SDS 확인</v>
+        <v>0.5 ppm</v>
       </c>
       <c r="Q15" t="str">
-        <v>제조사 SDS</v>
+        <v>ACGIH 또는 대표 참고값</v>
       </c>
       <c r="R15" t="str">
         <v>25 ppm</v>
@@ -2501,7 +2501,7 @@
         <v>ACGIH</v>
       </c>
       <c r="P16" t="str">
-        <v>1 ppm</v>
+        <v>0.5 ppm</v>
       </c>
       <c r="Q16" t="str">
         <v>NIOSH</v>
@@ -2635,7 +2635,7 @@
         <v>-</v>
       </c>
       <c r="P17" t="str">
-        <v>0.3 ppm</v>
+        <v>0.1 ppm</v>
       </c>
       <c r="Q17" t="str">
         <v>NIOSH</v>
@@ -2909,10 +2909,10 @@
         <v>-</v>
       </c>
       <c r="R19" t="str">
-        <v>800 ppm</v>
+        <v>제품 SDS 확인</v>
       </c>
       <c r="S19" t="str">
-        <v>대표 참고값</v>
+        <v>-</v>
       </c>
       <c r="T19" t="str">
         <v>공기보다 무거움</v>
@@ -4734,22 +4734,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B33" t="str">
-        <v>메탄올</v>
+        <v>이소프로필알코올</v>
       </c>
       <c r="C33" t="str">
-        <v>Methanol</v>
+        <v>Isopropyl Alcohol</v>
       </c>
       <c r="D33" t="str">
-        <v>CH3OH</v>
+        <v>C3H8O</v>
       </c>
       <c r="E33" t="str">
-        <v>67-56-1</v>
+        <v>67-63-0</v>
       </c>
       <c r="F33" t="str">
-        <v>메탄올, Methanol</v>
+        <v>IPA, 이소프로판올</v>
       </c>
       <c r="G33" t="str">
         <v>세정 / 용제</v>
@@ -4761,10 +4761,10 @@
         <v>고위험</v>
       </c>
       <c r="J33" t="str">
-        <v>🔥 인화성, ☠️ 급성독성</v>
+        <v>🔥 인화성, ❗ 경고</v>
       </c>
       <c r="K33" t="str">
-        <v>원액: 중성 (독성·인화성 우선)</v>
+        <v>원액: 중성 (인화성 우선)</v>
       </c>
       <c r="L33" t="str">
         <v>200 ppm</v>
@@ -4773,7 +4773,7 @@
         <v>OSHA</v>
       </c>
       <c r="N33" t="str">
-        <v>250 ppm</v>
+        <v>400 ppm</v>
       </c>
       <c r="O33" t="str">
         <v>ACGIH</v>
@@ -4785,7 +4785,7 @@
         <v>-</v>
       </c>
       <c r="R33" t="str">
-        <v>6000 ppm</v>
+        <v>2000 ppm</v>
       </c>
       <c r="S33" t="str">
         <v>NIOSH</v>
@@ -4794,43 +4794,43 @@
         <v>0.79 g/cm³</v>
       </c>
       <c r="U33" t="str">
-        <v>97 mmHg</v>
+        <v>45 mmHg</v>
       </c>
       <c r="V33" t="str">
-        <v>65°C</v>
+        <v>82°C</v>
       </c>
       <c r="W33" t="str">
-        <v>11°C</v>
+        <v>12°C</v>
       </c>
       <c r="X33" t="str">
-        <v>464°C</v>
+        <v>399°C</v>
       </c>
       <c r="Y33" t="str">
-        <v>6%</v>
+        <v>2%</v>
       </c>
       <c r="Z33" t="str">
-        <v>36%</v>
+        <v>12%</v>
       </c>
       <c r="AA33" t="str">
-        <v>고인화성, 시신경 독성, 흡입 독성</v>
+        <v>고인화성, 정전기 점화 가능, 증기 흡입 자극</v>
       </c>
       <c r="AB33" t="str">
         <v>물 혼합 가능</v>
       </c>
       <c r="AC33" t="str">
-        <v>흡착·환기 우선</v>
+        <v>흡착 및 환기 우선</v>
       </c>
       <c r="AD33" t="str">
         <v>산화제, 점화원</v>
       </c>
       <c r="AE33" t="str">
-        <v>흡착 및 회수 우선</v>
+        <v>흡착·회수 우선</v>
       </c>
       <c r="AF33" t="str">
         <v>가능</v>
       </c>
       <c r="AG33" t="str">
-        <v>물 사용 가능하나 인화성 고려</v>
+        <v>물 사용 가능</v>
       </c>
       <c r="AH33" t="str">
         <v>일반 중화 대상 아님</v>
@@ -4839,7 +4839,7 @@
         <v>유기증기용 호흡보호구, 방염 보호구</v>
       </c>
       <c r="AJ33" t="str">
-        <v>정전기·점화원 관리 중요</v>
+        <v>LEL 도달 가능성 주의</v>
       </c>
       <c r="AK33" t="str">
         <v>N</v>
@@ -4868,49 +4868,49 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B34" t="str">
-        <v>아세톤</v>
+        <v>질소</v>
       </c>
       <c r="C34" t="str">
-        <v>Acetone</v>
+        <v>Nitrogen</v>
       </c>
       <c r="D34" t="str">
-        <v>C3H6O</v>
+        <v>N2</v>
       </c>
       <c r="E34" t="str">
-        <v>67-64-1</v>
+        <v>7727-37-9</v>
       </c>
       <c r="F34" t="str">
-        <v>Acetone, 아세톤</v>
+        <v>N2, 질소</v>
       </c>
       <c r="G34" t="str">
-        <v>세정 / 용제</v>
+        <v>퍼지 / Utility</v>
       </c>
       <c r="H34" t="str">
-        <v>무색 액체</v>
+        <v>무색 기체</v>
       </c>
       <c r="I34" t="str">
         <v>주의</v>
       </c>
       <c r="J34" t="str">
-        <v>🔥 인화성</v>
+        <v>🧯 가스실린더</v>
       </c>
       <c r="K34" t="str">
-        <v>원액: 중성 (인화성 우선)</v>
+        <v>가스: 해당 없음 (산소결핍 위험)</v>
       </c>
       <c r="L34" t="str">
-        <v>250 ppm</v>
+        <v>단순 질식성</v>
       </c>
       <c r="M34" t="str">
-        <v>OSHA</v>
+        <v>NIOSH</v>
       </c>
       <c r="N34" t="str">
-        <v>500 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="O34" t="str">
-        <v>ACGIH</v>
+        <v>-</v>
       </c>
       <c r="P34" t="str">
         <v>설정 없음</v>
@@ -4919,67 +4919,67 @@
         <v>-</v>
       </c>
       <c r="R34" t="str">
-        <v>2500 ppm</v>
+        <v>단순 질식성</v>
       </c>
       <c r="S34" t="str">
         <v>NIOSH</v>
       </c>
       <c r="T34" t="str">
-        <v>0.79 g/cm³</v>
+        <v>공기보다 약간 가벼움</v>
       </c>
       <c r="U34" t="str">
-        <v>180 mmHg</v>
+        <v>가스</v>
       </c>
       <c r="V34" t="str">
-        <v>56°C</v>
+        <v>-196°C</v>
       </c>
       <c r="W34" t="str">
-        <v>-20°C</v>
+        <v>비가연성</v>
       </c>
       <c r="X34" t="str">
-        <v>465°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y34" t="str">
-        <v>2.6%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z34" t="str">
-        <v>12.8%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA34" t="str">
-        <v>고인화성, 증기 흡입 자극</v>
+        <v>산소결핍, 밀폐공간 질식 위험</v>
       </c>
       <c r="AB34" t="str">
-        <v>물 혼합 가능</v>
+        <v>물반응성 낮음</v>
       </c>
       <c r="AC34" t="str">
-        <v>흡착 및 환기 우선</v>
+        <v>환기 우선</v>
       </c>
       <c r="AD34" t="str">
-        <v>산화제, 점화원</v>
+        <v/>
       </c>
       <c r="AE34" t="str">
-        <v>흡착·회수 우선</v>
+        <v>중화 대상 아님</v>
       </c>
       <c r="AF34" t="str">
-        <v>가능</v>
+        <v>확인 필요</v>
       </c>
       <c r="AG34" t="str">
-        <v>물 사용 가능</v>
+        <v>물 사용 효과 없음</v>
       </c>
       <c r="AH34" t="str">
-        <v>일반 중화 대상 아님</v>
+        <v>산소농도 관리 우선</v>
       </c>
       <c r="AI34" t="str">
-        <v>유기증기용 호흡보호구, 방염 보호구</v>
+        <v>산소농도측정기, 공기호흡기</v>
       </c>
       <c r="AJ34" t="str">
-        <v>LEL 관리 중요</v>
+        <v>무취·무색이라 감지 어려움</v>
       </c>
       <c r="AK34" t="str">
         <v>N</v>
       </c>
       <c r="AL34" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM34" t="str">
         <v>N</v>
@@ -5002,49 +5002,49 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B35" t="str">
-        <v>이소프로필알코올</v>
+        <v>헬륨</v>
       </c>
       <c r="C35" t="str">
-        <v>Isopropyl Alcohol</v>
+        <v>Helium</v>
       </c>
       <c r="D35" t="str">
-        <v>C3H8O</v>
+        <v>He</v>
       </c>
       <c r="E35" t="str">
-        <v>67-63-0</v>
+        <v>7440-59-7</v>
       </c>
       <c r="F35" t="str">
-        <v>IPA, 이소프로판올</v>
+        <v>He, 헬륨</v>
       </c>
       <c r="G35" t="str">
-        <v>세정 / 용제</v>
+        <v>Leak Test / Utility</v>
       </c>
       <c r="H35" t="str">
-        <v>무색 액체</v>
+        <v>무색 기체</v>
       </c>
       <c r="I35" t="str">
-        <v>고위험</v>
+        <v>주의</v>
       </c>
       <c r="J35" t="str">
-        <v>🔥 인화성, ❗ 경고</v>
+        <v>🧯 가스실린더</v>
       </c>
       <c r="K35" t="str">
-        <v>원액: 중성 (인화성 우선)</v>
+        <v>가스: 해당 없음 (질식 위험 가능)</v>
       </c>
       <c r="L35" t="str">
-        <v>200 ppm</v>
+        <v>단순 질식성</v>
       </c>
       <c r="M35" t="str">
-        <v>OSHA</v>
+        <v>NIOSH</v>
       </c>
       <c r="N35" t="str">
-        <v>400 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="O35" t="str">
-        <v>ACGIH</v>
+        <v>-</v>
       </c>
       <c r="P35" t="str">
         <v>설정 없음</v>
@@ -5053,61 +5053,61 @@
         <v>-</v>
       </c>
       <c r="R35" t="str">
-        <v>2000 ppm</v>
+        <v>단순 질식성</v>
       </c>
       <c r="S35" t="str">
         <v>NIOSH</v>
       </c>
       <c r="T35" t="str">
-        <v>0.79 g/cm³</v>
+        <v>공기보다 매우 가벼움</v>
       </c>
       <c r="U35" t="str">
-        <v>45 mmHg</v>
+        <v>가스</v>
       </c>
       <c r="V35" t="str">
-        <v>82°C</v>
+        <v>-269°C</v>
       </c>
       <c r="W35" t="str">
-        <v>12°C</v>
+        <v>비가연성</v>
       </c>
       <c r="X35" t="str">
-        <v>399°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y35" t="str">
-        <v>2%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z35" t="str">
-        <v>12%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA35" t="str">
-        <v>고인화성, 정전기 점화 가능, 증기 흡입 자극</v>
+        <v>산소결핍, 고압가스 위험</v>
       </c>
       <c r="AB35" t="str">
-        <v>물 혼합 가능</v>
+        <v>반응성 낮음</v>
       </c>
       <c r="AC35" t="str">
-        <v>흡착 및 환기 우선</v>
+        <v>환기 우선</v>
       </c>
       <c r="AD35" t="str">
-        <v>산화제, 점화원</v>
+        <v/>
       </c>
       <c r="AE35" t="str">
-        <v>흡착·회수 우선</v>
+        <v>중화 대상 아님</v>
       </c>
       <c r="AF35" t="str">
-        <v>가능</v>
+        <v>확인 필요</v>
       </c>
       <c r="AG35" t="str">
-        <v>물 사용 가능</v>
+        <v>효과 없음</v>
       </c>
       <c r="AH35" t="str">
-        <v>일반 중화 대상 아님</v>
+        <v>환기 우선</v>
       </c>
       <c r="AI35" t="str">
-        <v>유기증기용 호흡보호구, 방염 보호구</v>
+        <v>산소농도측정기</v>
       </c>
       <c r="AJ35" t="str">
-        <v>LEL 도달 가능성 주의</v>
+        <v>밀폐공간 산소결핍 주의</v>
       </c>
       <c r="AK35" t="str">
         <v>N</v>
@@ -5136,25 +5136,25 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" t="str">
-        <v>질소</v>
+        <v>아르곤</v>
       </c>
       <c r="C36" t="str">
-        <v>Nitrogen</v>
+        <v>Argon</v>
       </c>
       <c r="D36" t="str">
-        <v>N2</v>
+        <v>Ar</v>
       </c>
       <c r="E36" t="str">
-        <v>7727-37-9</v>
+        <v>7440-37-1</v>
       </c>
       <c r="F36" t="str">
-        <v>N2, 질소</v>
+        <v>Ar, 아르곤</v>
       </c>
       <c r="G36" t="str">
-        <v>퍼지 / Utility</v>
+        <v>퍼지 / 용접 / Utility</v>
       </c>
       <c r="H36" t="str">
         <v>무색 기체</v>
@@ -5166,7 +5166,7 @@
         <v>🧯 가스실린더</v>
       </c>
       <c r="K36" t="str">
-        <v>가스: 해당 없음 (산소결핍 위험)</v>
+        <v>가스: 해당 없음 (질식 위험)</v>
       </c>
       <c r="L36" t="str">
         <v>단순 질식성</v>
@@ -5193,13 +5193,13 @@
         <v>NIOSH</v>
       </c>
       <c r="T36" t="str">
-        <v>공기보다 약간 가벼움</v>
+        <v>공기보다 무거움</v>
       </c>
       <c r="U36" t="str">
         <v>가스</v>
       </c>
       <c r="V36" t="str">
-        <v>-196°C</v>
+        <v>-186°C</v>
       </c>
       <c r="W36" t="str">
         <v>비가연성</v>
@@ -5214,10 +5214,10 @@
         <v>해당 없음</v>
       </c>
       <c r="AA36" t="str">
-        <v>산소결핍, 밀폐공간 질식 위험</v>
+        <v>저지대 산소결핍, 밀폐공간 질식 위험</v>
       </c>
       <c r="AB36" t="str">
-        <v>물반응성 낮음</v>
+        <v>반응성 낮음</v>
       </c>
       <c r="AC36" t="str">
         <v>환기 우선</v>
@@ -5232,7 +5232,7 @@
         <v>확인 필요</v>
       </c>
       <c r="AG36" t="str">
-        <v>물 사용 효과 없음</v>
+        <v>효과 없음</v>
       </c>
       <c r="AH36" t="str">
         <v>산소농도 관리 우선</v>
@@ -5241,10 +5241,10 @@
         <v>산소농도측정기, 공기호흡기</v>
       </c>
       <c r="AJ36" t="str">
-        <v>무취·무색이라 감지 어려움</v>
+        <v>저지대 체류 가능</v>
       </c>
       <c r="AK36" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AL36" t="str">
         <v>Y</v>
@@ -5265,78 +5265,78 @@
         <v>N</v>
       </c>
       <c r="AR36" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B37" t="str">
-        <v>헬륨</v>
+        <v>산소</v>
       </c>
       <c r="C37" t="str">
-        <v>Helium</v>
+        <v>Oxygen</v>
       </c>
       <c r="D37" t="str">
-        <v>He</v>
+        <v>O2</v>
       </c>
       <c r="E37" t="str">
-        <v>7440-59-7</v>
+        <v>7782-44-7</v>
       </c>
       <c r="F37" t="str">
-        <v>He, 헬륨</v>
+        <v>O2, 산소</v>
       </c>
       <c r="G37" t="str">
-        <v>Leak Test / Utility</v>
+        <v>Utility</v>
       </c>
       <c r="H37" t="str">
         <v>무색 기체</v>
       </c>
       <c r="I37" t="str">
-        <v>주의</v>
+        <v>고위험</v>
       </c>
       <c r="J37" t="str">
-        <v>🧯 가스실린더</v>
+        <v>⭕ 산화성, 🧯 가스실린더</v>
       </c>
       <c r="K37" t="str">
-        <v>가스: 해당 없음 (질식 위험 가능)</v>
+        <v>가스: 해당 없음 (산화성)</v>
       </c>
       <c r="L37" t="str">
-        <v>단순 질식성</v>
+        <v>해당 없음</v>
       </c>
       <c r="M37" t="str">
-        <v>NIOSH</v>
+        <v>-</v>
       </c>
       <c r="N37" t="str">
-        <v>설정 없음</v>
+        <v>해당 없음</v>
       </c>
       <c r="O37" t="str">
         <v>-</v>
       </c>
       <c r="P37" t="str">
-        <v>설정 없음</v>
+        <v>해당 없음</v>
       </c>
       <c r="Q37" t="str">
         <v>-</v>
       </c>
       <c r="R37" t="str">
-        <v>단순 질식성</v>
+        <v>해당 없음</v>
       </c>
       <c r="S37" t="str">
-        <v>NIOSH</v>
+        <v>-</v>
       </c>
       <c r="T37" t="str">
-        <v>공기보다 매우 가벼움</v>
+        <v>공기보다 약간 무거움</v>
       </c>
       <c r="U37" t="str">
         <v>가스</v>
       </c>
       <c r="V37" t="str">
-        <v>-269°C</v>
+        <v>-183°C</v>
       </c>
       <c r="W37" t="str">
-        <v>비가연성</v>
+        <v>산화성</v>
       </c>
       <c r="X37" t="str">
         <v>해당 없음</v>
@@ -5348,34 +5348,34 @@
         <v>해당 없음</v>
       </c>
       <c r="AA37" t="str">
-        <v>산소결핍, 고압가스 위험</v>
+        <v>연소 촉진, 산소농도 증가 시 화재 위험 급증</v>
       </c>
       <c r="AB37" t="str">
         <v>반응성 낮음</v>
       </c>
       <c r="AC37" t="str">
-        <v>환기 우선</v>
+        <v>차단 및 환기 우선</v>
       </c>
       <c r="AD37" t="str">
-        <v/>
+        <v>가연물, 유류</v>
       </c>
       <c r="AE37" t="str">
+        <v>산소농도 저감 우선</v>
+      </c>
+      <c r="AF37" t="str">
+        <v>가능</v>
+      </c>
+      <c r="AG37" t="str">
+        <v>일반적 사용 가능</v>
+      </c>
+      <c r="AH37" t="str">
         <v>중화 대상 아님</v>
       </c>
-      <c r="AF37" t="str">
-        <v>확인 필요</v>
-      </c>
-      <c r="AG37" t="str">
-        <v>효과 없음</v>
-      </c>
-      <c r="AH37" t="str">
-        <v>환기 우선</v>
-      </c>
       <c r="AI37" t="str">
-        <v>산소농도측정기</v>
+        <v>방염 보호구</v>
       </c>
       <c r="AJ37" t="str">
-        <v>밀폐공간 산소결핍 주의</v>
+        <v>산소농도 상승 시 화재폭발 위험 증가</v>
       </c>
       <c r="AK37" t="str">
         <v>N</v>
@@ -5384,13 +5384,13 @@
         <v>N</v>
       </c>
       <c r="AM37" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN37" t="str">
         <v>Y</v>
       </c>
       <c r="AO37" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP37" t="str">
         <v>N</v>
@@ -5404,25 +5404,25 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" t="str">
-        <v>아르곤</v>
+        <v>이산화탄소</v>
       </c>
       <c r="C38" t="str">
-        <v>Argon</v>
+        <v>Carbon Dioxide</v>
       </c>
       <c r="D38" t="str">
-        <v>Ar</v>
+        <v>CO2</v>
       </c>
       <c r="E38" t="str">
-        <v>7440-37-1</v>
+        <v>124-38-9</v>
       </c>
       <c r="F38" t="str">
-        <v>Ar, 아르곤</v>
+        <v>CO2, 이산화탄소</v>
       </c>
       <c r="G38" t="str">
-        <v>퍼지 / 용접 / Utility</v>
+        <v>소화설비 / Utility</v>
       </c>
       <c r="H38" t="str">
         <v>무색 기체</v>
@@ -5434,28 +5434,28 @@
         <v>🧯 가스실린더</v>
       </c>
       <c r="K38" t="str">
-        <v>가스: 해당 없음 (질식 위험)</v>
+        <v>가스: 약산성 가능 (고농도 질식 위험)</v>
       </c>
       <c r="L38" t="str">
-        <v>단순 질식성</v>
+        <v>5000 ppm</v>
       </c>
       <c r="M38" t="str">
+        <v>OSHA</v>
+      </c>
+      <c r="N38" t="str">
+        <v>30000 ppm</v>
+      </c>
+      <c r="O38" t="str">
+        <v>ACGIH</v>
+      </c>
+      <c r="P38" t="str">
+        <v>40000 ppm</v>
+      </c>
+      <c r="Q38" t="str">
         <v>NIOSH</v>
       </c>
-      <c r="N38" t="str">
-        <v>설정 없음</v>
-      </c>
-      <c r="O38" t="str">
-        <v>-</v>
-      </c>
-      <c r="P38" t="str">
-        <v>설정 없음</v>
-      </c>
-      <c r="Q38" t="str">
-        <v>-</v>
-      </c>
       <c r="R38" t="str">
-        <v>단순 질식성</v>
+        <v>40000 ppm</v>
       </c>
       <c r="S38" t="str">
         <v>NIOSH</v>
@@ -5467,7 +5467,7 @@
         <v>가스</v>
       </c>
       <c r="V38" t="str">
-        <v>-186°C</v>
+        <v>-78°C (승화)</v>
       </c>
       <c r="W38" t="str">
         <v>비가연성</v>
@@ -5482,10 +5482,10 @@
         <v>해당 없음</v>
       </c>
       <c r="AA38" t="str">
-        <v>저지대 산소결핍, 밀폐공간 질식 위험</v>
+        <v>산소결핍, 저지대 체류 가능</v>
       </c>
       <c r="AB38" t="str">
-        <v>반응성 낮음</v>
+        <v>물에 녹아 약산성 가능</v>
       </c>
       <c r="AC38" t="str">
         <v>환기 우선</v>
@@ -5494,22 +5494,22 @@
         <v/>
       </c>
       <c r="AE38" t="str">
+        <v>환기 및 산소농도 확보</v>
+      </c>
+      <c r="AF38" t="str">
+        <v>가능</v>
+      </c>
+      <c r="AG38" t="str">
+        <v>효과 제한적</v>
+      </c>
+      <c r="AH38" t="str">
         <v>중화 대상 아님</v>
       </c>
-      <c r="AF38" t="str">
-        <v>확인 필요</v>
-      </c>
-      <c r="AG38" t="str">
-        <v>효과 없음</v>
-      </c>
-      <c r="AH38" t="str">
-        <v>산소농도 관리 우선</v>
-      </c>
       <c r="AI38" t="str">
-        <v>산소농도측정기, 공기호흡기</v>
+        <v>공기호흡기</v>
       </c>
       <c r="AJ38" t="str">
-        <v>저지대 체류 가능</v>
+        <v>밀폐공간 질식 위험</v>
       </c>
       <c r="AK38" t="str">
         <v>Y</v>
@@ -5538,127 +5538,127 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B39" t="str">
-        <v>산소</v>
+        <v>일산화탄소</v>
       </c>
       <c r="C39" t="str">
-        <v>Oxygen</v>
+        <v>Carbon Monoxide</v>
       </c>
       <c r="D39" t="str">
-        <v>O2</v>
+        <v>CO</v>
       </c>
       <c r="E39" t="str">
-        <v>7782-44-7</v>
+        <v>630-08-0</v>
       </c>
       <c r="F39" t="str">
-        <v>O2, 산소</v>
+        <v>CO, 일산화탄소</v>
       </c>
       <c r="G39" t="str">
-        <v>Utility</v>
+        <v>연소 / Utility</v>
       </c>
       <c r="H39" t="str">
         <v>무색 기체</v>
       </c>
       <c r="I39" t="str">
-        <v>고위험</v>
+        <v>매우 위험</v>
       </c>
       <c r="J39" t="str">
-        <v>⭕ 산화성, 🧯 가스실린더</v>
+        <v>☠️ 급성독성, 🔥 인화성</v>
       </c>
       <c r="K39" t="str">
-        <v>가스: 해당 없음 (산화성)</v>
+        <v>가스: 해당 없음 (혈액 독성)</v>
       </c>
       <c r="L39" t="str">
-        <v>해당 없음</v>
+        <v>25 ppm</v>
       </c>
       <c r="M39" t="str">
-        <v>-</v>
+        <v>OSHA</v>
       </c>
       <c r="N39" t="str">
-        <v>해당 없음</v>
+        <v>200 ppm</v>
       </c>
       <c r="O39" t="str">
-        <v>-</v>
+        <v>대표 참고값</v>
       </c>
       <c r="P39" t="str">
-        <v>해당 없음</v>
+        <v>200 ppm</v>
       </c>
       <c r="Q39" t="str">
-        <v>-</v>
+        <v>NIOSH</v>
       </c>
       <c r="R39" t="str">
-        <v>해당 없음</v>
+        <v>1200 ppm</v>
       </c>
       <c r="S39" t="str">
-        <v>-</v>
+        <v>NIOSH</v>
       </c>
       <c r="T39" t="str">
-        <v>공기보다 약간 무거움</v>
+        <v>공기보다 약간 가벼움</v>
       </c>
       <c r="U39" t="str">
         <v>가스</v>
       </c>
       <c r="V39" t="str">
-        <v>-183°C</v>
+        <v>-191°C</v>
       </c>
       <c r="W39" t="str">
-        <v>산화성</v>
+        <v>가연성</v>
       </c>
       <c r="X39" t="str">
-        <v>해당 없음</v>
+        <v>609°C</v>
       </c>
       <c r="Y39" t="str">
-        <v>해당 없음</v>
+        <v>12.5%</v>
       </c>
       <c r="Z39" t="str">
-        <v>해당 없음</v>
+        <v>74%</v>
       </c>
       <c r="AA39" t="str">
-        <v>연소 촉진, 산소농도 증가 시 화재 위험 급증</v>
+        <v>헤모글로빈 결합 독성, 무취·무색, 가연성</v>
       </c>
       <c r="AB39" t="str">
         <v>반응성 낮음</v>
       </c>
       <c r="AC39" t="str">
-        <v>차단 및 환기 우선</v>
+        <v>환기 및 차단 우선</v>
       </c>
       <c r="AD39" t="str">
-        <v>가연물, 유류</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE39" t="str">
-        <v>산소농도 저감 우선</v>
+        <v>환기 및 연소 차단</v>
       </c>
       <c r="AF39" t="str">
-        <v>가능</v>
+        <v>확인 필요</v>
       </c>
       <c r="AG39" t="str">
-        <v>일반적 사용 가능</v>
+        <v>효과 제한적</v>
       </c>
       <c r="AH39" t="str">
         <v>중화 대상 아님</v>
       </c>
       <c r="AI39" t="str">
-        <v>방염 보호구</v>
+        <v>공기호흡기, CO 측정기</v>
       </c>
       <c r="AJ39" t="str">
-        <v>산소농도 상승 시 화재폭발 위험 증가</v>
+        <v>무취라 감지 어려움</v>
       </c>
       <c r="AK39" t="str">
         <v>N</v>
       </c>
       <c r="AL39" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM39" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AN39" t="str">
         <v>Y</v>
       </c>
       <c r="AO39" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AP39" t="str">
         <v>N</v>
@@ -5672,58 +5672,58 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B40" t="str">
-        <v>이산화탄소</v>
+        <v>황화수소</v>
       </c>
       <c r="C40" t="str">
-        <v>Carbon Dioxide</v>
+        <v>Hydrogen Sulfide</v>
       </c>
       <c r="D40" t="str">
-        <v>CO2</v>
+        <v>H2S</v>
       </c>
       <c r="E40" t="str">
-        <v>124-38-9</v>
+        <v>7783-06-4</v>
       </c>
       <c r="F40" t="str">
-        <v>CO2, 이산화탄소</v>
+        <v>H2S, 황화수소</v>
       </c>
       <c r="G40" t="str">
-        <v>소화설비 / Utility</v>
+        <v>폐수 / Utility</v>
       </c>
       <c r="H40" t="str">
         <v>무색 기체</v>
       </c>
       <c r="I40" t="str">
-        <v>주의</v>
+        <v>매우 위험</v>
       </c>
       <c r="J40" t="str">
-        <v>🧯 가스실린더</v>
+        <v>☠️ 급성독성, 🔥 인화성</v>
       </c>
       <c r="K40" t="str">
-        <v>가스: 약산성 가능 (고농도 질식 위험)</v>
+        <v>가스: 약산성 가능 (고독성)</v>
       </c>
       <c r="L40" t="str">
-        <v>5000 ppm</v>
+        <v>1 ppm</v>
       </c>
       <c r="M40" t="str">
-        <v>OSHA</v>
+        <v>ACGIH</v>
       </c>
       <c r="N40" t="str">
-        <v>30000 ppm</v>
+        <v>5 ppm</v>
       </c>
       <c r="O40" t="str">
         <v>ACGIH</v>
       </c>
       <c r="P40" t="str">
-        <v>40000 ppm</v>
+        <v>10 ppm</v>
       </c>
       <c r="Q40" t="str">
         <v>NIOSH</v>
       </c>
       <c r="R40" t="str">
-        <v>40000 ppm</v>
+        <v>100 ppm</v>
       </c>
       <c r="S40" t="str">
         <v>NIOSH</v>
@@ -5735,49 +5735,49 @@
         <v>가스</v>
       </c>
       <c r="V40" t="str">
-        <v>-78°C (승화)</v>
+        <v>-60°C</v>
       </c>
       <c r="W40" t="str">
-        <v>비가연성</v>
+        <v>가연성</v>
       </c>
       <c r="X40" t="str">
-        <v>해당 없음</v>
+        <v>260°C</v>
       </c>
       <c r="Y40" t="str">
-        <v>해당 없음</v>
+        <v>4%</v>
       </c>
       <c r="Z40" t="str">
-        <v>해당 없음</v>
+        <v>44%</v>
       </c>
       <c r="AA40" t="str">
-        <v>산소결핍, 저지대 체류 가능</v>
+        <v>후각 마비 가능, 고독성, 저지대 체류</v>
       </c>
       <c r="AB40" t="str">
-        <v>물에 녹아 약산성 가능</v>
+        <v>산성 조건 발생 가능</v>
       </c>
       <c r="AC40" t="str">
-        <v>환기 우선</v>
+        <v>환기·차단 우선</v>
       </c>
       <c r="AD40" t="str">
-        <v/>
+        <v>산화제</v>
       </c>
       <c r="AE40" t="str">
-        <v>환기 및 산소농도 확보</v>
+        <v>가스 차단 및 스크러빙</v>
       </c>
       <c r="AF40" t="str">
         <v>가능</v>
       </c>
       <c r="AG40" t="str">
-        <v>효과 제한적</v>
+        <v>일부 가능</v>
       </c>
       <c r="AH40" t="str">
-        <v>중화 대상 아님</v>
+        <v>전용 처리 검토</v>
       </c>
       <c r="AI40" t="str">
-        <v>공기호흡기</v>
+        <v>공기호흡기, H2S 측정기</v>
       </c>
       <c r="AJ40" t="str">
-        <v>밀폐공간 질식 위험</v>
+        <v>냄새 사라져도 안전 의미 아님</v>
       </c>
       <c r="AK40" t="str">
         <v>Y</v>
@@ -5806,22 +5806,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B41" t="str">
-        <v>일산화탄소</v>
+        <v>이산화황</v>
       </c>
       <c r="C41" t="str">
-        <v>Carbon Monoxide</v>
+        <v>Sulfur Dioxide</v>
       </c>
       <c r="D41" t="str">
-        <v>CO</v>
+        <v>SO2</v>
       </c>
       <c r="E41" t="str">
-        <v>630-08-0</v>
+        <v>7446-09-5</v>
       </c>
       <c r="F41" t="str">
-        <v>CO, 일산화탄소</v>
+        <v>SO2, 이산화황</v>
       </c>
       <c r="G41" t="str">
         <v>연소 / Utility</v>
@@ -5830,91 +5830,91 @@
         <v>무색 기체</v>
       </c>
       <c r="I41" t="str">
-        <v>매우 위험</v>
+        <v>고위험</v>
       </c>
       <c r="J41" t="str">
-        <v>☠️ 급성독성, 🔥 인화성</v>
+        <v>☠️ 급성독성, 🧪 부식성</v>
       </c>
       <c r="K41" t="str">
-        <v>가스: 해당 없음 (혈액 독성)</v>
+        <v>수분 접촉: 산성 (자극성 가스)</v>
       </c>
       <c r="L41" t="str">
-        <v>25 ppm</v>
+        <v>2 ppm</v>
       </c>
       <c r="M41" t="str">
         <v>OSHA</v>
       </c>
       <c r="N41" t="str">
-        <v>200 ppm</v>
+        <v>5 ppm</v>
       </c>
       <c r="O41" t="str">
-        <v>대표 참고값</v>
+        <v>ACGIH</v>
       </c>
       <c r="P41" t="str">
-        <v>200 ppm</v>
+        <v>5 ppm</v>
       </c>
       <c r="Q41" t="str">
         <v>NIOSH</v>
       </c>
       <c r="R41" t="str">
-        <v>1200 ppm</v>
+        <v>100 ppm</v>
       </c>
       <c r="S41" t="str">
         <v>NIOSH</v>
       </c>
       <c r="T41" t="str">
-        <v>공기보다 약간 가벼움</v>
+        <v>공기보다 무거움</v>
       </c>
       <c r="U41" t="str">
         <v>가스</v>
       </c>
       <c r="V41" t="str">
-        <v>-191°C</v>
+        <v>-10°C</v>
       </c>
       <c r="W41" t="str">
-        <v>가연성</v>
+        <v>비가연성</v>
       </c>
       <c r="X41" t="str">
-        <v>609°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y41" t="str">
-        <v>12.5%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z41" t="str">
-        <v>74%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA41" t="str">
-        <v>헤모글로빈 결합 독성, 무취·무색, 가연성</v>
+        <v>호흡기 자극, 산성 가스, 저지대 체류 가능</v>
       </c>
       <c r="AB41" t="str">
-        <v>반응성 낮음</v>
+        <v>물과 반응해 산성화 가능</v>
       </c>
       <c r="AC41" t="str">
-        <v>환기 및 차단 우선</v>
+        <v>환기 및 물 세척 가능</v>
       </c>
       <c r="AD41" t="str">
-        <v>산화제, 점화원</v>
+        <v>산화제</v>
       </c>
       <c r="AE41" t="str">
-        <v>환기 및 연소 차단</v>
+        <v>알칼리 흡수 검토</v>
       </c>
       <c r="AF41" t="str">
-        <v>확인 필요</v>
+        <v>가능</v>
       </c>
       <c r="AG41" t="str">
-        <v>효과 제한적</v>
+        <v>물 사용 가능</v>
       </c>
       <c r="AH41" t="str">
-        <v>중화 대상 아님</v>
+        <v>알칼리 중화 검토</v>
       </c>
       <c r="AI41" t="str">
-        <v>공기호흡기, CO 측정기</v>
+        <v>공기호흡기, 내산 장갑</v>
       </c>
       <c r="AJ41" t="str">
-        <v>무취라 감지 어려움</v>
+        <v>저지대 체류 가능</v>
       </c>
       <c r="AK41" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AL41" t="str">
         <v>Y</v>
@@ -5935,123 +5935,123 @@
         <v>N</v>
       </c>
       <c r="AR41" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B42" t="str">
-        <v>황화수소</v>
+        <v>붕산</v>
       </c>
       <c r="C42" t="str">
-        <v>Hydrogen Sulfide</v>
+        <v>Boric Acid</v>
       </c>
       <c r="D42" t="str">
-        <v>H2S</v>
+        <v>H3BO3</v>
       </c>
       <c r="E42" t="str">
-        <v>7783-06-4</v>
+        <v>10043-35-3</v>
       </c>
       <c r="F42" t="str">
-        <v>H2S, 황화수소</v>
+        <v>붕산, Boric Acid</v>
       </c>
       <c r="G42" t="str">
-        <v>폐수 / Utility</v>
+        <v>폐수 / 화학처리</v>
       </c>
       <c r="H42" t="str">
-        <v>무색 기체</v>
+        <v>백색 고체</v>
       </c>
       <c r="I42" t="str">
-        <v>매우 위험</v>
+        <v>주의</v>
       </c>
       <c r="J42" t="str">
-        <v>☠️ 급성독성, 🔥 인화성</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K42" t="str">
-        <v>가스: 약산성 가능 (고독성)</v>
+        <v>용액: 약산성 (저농도 자극 가능)</v>
       </c>
       <c r="L42" t="str">
-        <v>1 ppm</v>
+        <v>10 mg/m³</v>
       </c>
       <c r="M42" t="str">
-        <v>ACGIH</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N42" t="str">
-        <v>5 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="O42" t="str">
-        <v>ACGIH</v>
+        <v>-</v>
       </c>
       <c r="P42" t="str">
-        <v>10 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q42" t="str">
-        <v>NIOSH</v>
+        <v>-</v>
       </c>
       <c r="R42" t="str">
-        <v>100 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="S42" t="str">
-        <v>NIOSH</v>
+        <v>-</v>
       </c>
       <c r="T42" t="str">
-        <v>공기보다 무거움</v>
+        <v>1.43 g/cm³</v>
       </c>
       <c r="U42" t="str">
-        <v>가스</v>
+        <v>낮음</v>
       </c>
       <c r="V42" t="str">
-        <v>-60°C</v>
+        <v>분해</v>
       </c>
       <c r="W42" t="str">
-        <v>가연성</v>
+        <v>비가연성</v>
       </c>
       <c r="X42" t="str">
-        <v>260°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y42" t="str">
-        <v>4%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z42" t="str">
-        <v>44%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA42" t="str">
-        <v>후각 마비 가능, 고독성, 저지대 체류</v>
+        <v>분진 자극 가능</v>
       </c>
       <c r="AB42" t="str">
-        <v>산성 조건 발생 가능</v>
+        <v>수용성</v>
       </c>
       <c r="AC42" t="str">
-        <v>환기·차단 우선</v>
+        <v>물 세척 가능</v>
       </c>
       <c r="AD42" t="str">
-        <v>산화제</v>
+        <v>강염기</v>
       </c>
       <c r="AE42" t="str">
-        <v>가스 차단 및 스크러빙</v>
+        <v>일반 희석 및 세척</v>
       </c>
       <c r="AF42" t="str">
         <v>가능</v>
       </c>
       <c r="AG42" t="str">
-        <v>일부 가능</v>
+        <v>가능</v>
       </c>
       <c r="AH42" t="str">
-        <v>전용 처리 검토</v>
+        <v>일반 중화 불필요</v>
       </c>
       <c r="AI42" t="str">
-        <v>공기호흡기, H2S 측정기</v>
+        <v>보안경, 장갑</v>
       </c>
       <c r="AJ42" t="str">
-        <v>냄새 사라져도 안전 의미 아님</v>
+        <v>분진 흡입 주의</v>
       </c>
       <c r="AK42" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AL42" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM42" t="str">
         <v>N</v>
@@ -6069,75 +6069,75 @@
         <v>N</v>
       </c>
       <c r="AR42" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B43" t="str">
-        <v>이산화황</v>
+        <v>불화수소암모늄</v>
       </c>
       <c r="C43" t="str">
-        <v>Sulfur Dioxide</v>
+        <v>Ammonium Bifluoride</v>
       </c>
       <c r="D43" t="str">
-        <v>SO2</v>
+        <v>NH4HF2</v>
       </c>
       <c r="E43" t="str">
-        <v>7446-09-5</v>
+        <v>1341-49-7</v>
       </c>
       <c r="F43" t="str">
-        <v>SO2, 이산화황</v>
+        <v>ABF, 불화수소암모늄</v>
       </c>
       <c r="G43" t="str">
-        <v>연소 / Utility</v>
+        <v>Etch / 세정</v>
       </c>
       <c r="H43" t="str">
-        <v>무색 기체</v>
+        <v>백색 고체</v>
       </c>
       <c r="I43" t="str">
-        <v>고위험</v>
+        <v>매우 위험</v>
       </c>
       <c r="J43" t="str">
         <v>☠️ 급성독성, 🧪 부식성</v>
       </c>
       <c r="K43" t="str">
-        <v>수분 접촉: 산성 (자극성 가스)</v>
+        <v>용액: 산성 (HF 생성 가능)</v>
       </c>
       <c r="L43" t="str">
-        <v>2 ppm</v>
+        <v>2.5 mg/m³</v>
       </c>
       <c r="M43" t="str">
-        <v>OSHA</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N43" t="str">
-        <v>5 ppm</v>
+        <v>5 mg/m³</v>
       </c>
       <c r="O43" t="str">
-        <v>ACGIH</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="P43" t="str">
-        <v>5 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q43" t="str">
-        <v>NIOSH</v>
+        <v>-</v>
       </c>
       <c r="R43" t="str">
-        <v>100 ppm</v>
+        <v>제품 SDS 확인</v>
       </c>
       <c r="S43" t="str">
-        <v>NIOSH</v>
+        <v>제조사 SDS</v>
       </c>
       <c r="T43" t="str">
-        <v>공기보다 무거움</v>
+        <v>1.5 g/cm³</v>
       </c>
       <c r="U43" t="str">
-        <v>가스</v>
+        <v>낮음</v>
       </c>
       <c r="V43" t="str">
-        <v>-10°C</v>
+        <v>분해</v>
       </c>
       <c r="W43" t="str">
         <v>비가연성</v>
@@ -6152,37 +6152,37 @@
         <v>해당 없음</v>
       </c>
       <c r="AA43" t="str">
-        <v>호흡기 자극, 산성 가스, 저지대 체류 가능</v>
+        <v>HF 유사 위험성, 피부 침투 독성 가능</v>
       </c>
       <c r="AB43" t="str">
-        <v>물과 반응해 산성화 가능</v>
+        <v>물에 용해됨</v>
       </c>
       <c r="AC43" t="str">
-        <v>환기 및 물 세척 가능</v>
+        <v>대량 물 세척 가능</v>
       </c>
       <c r="AD43" t="str">
-        <v>산화제</v>
+        <v>강산, 금속</v>
       </c>
       <c r="AE43" t="str">
-        <v>알칼리 흡수 검토</v>
+        <v>칼슘계 중화 검토</v>
       </c>
       <c r="AF43" t="str">
         <v>가능</v>
       </c>
       <c r="AG43" t="str">
-        <v>물 사용 가능</v>
+        <v>가능</v>
       </c>
       <c r="AH43" t="str">
-        <v>알칼리 중화 검토</v>
+        <v>불소계 중화 검토</v>
       </c>
       <c r="AI43" t="str">
         <v>공기호흡기, 내산 장갑</v>
       </c>
       <c r="AJ43" t="str">
-        <v>저지대 체류 가능</v>
+        <v>HF 대응 수준 고려</v>
       </c>
       <c r="AK43" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AL43" t="str">
         <v>Y</v>
@@ -6197,81 +6197,81 @@
         <v>N</v>
       </c>
       <c r="AP43" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AQ43" t="str">
         <v>N</v>
       </c>
       <c r="AR43" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B44" t="str">
-        <v>붕산</v>
+        <v>인산</v>
       </c>
       <c r="C44" t="str">
-        <v>Boric Acid</v>
+        <v>Phosphoric Acid</v>
       </c>
       <c r="D44" t="str">
-        <v>H3BO3</v>
+        <v>H3PO4</v>
       </c>
       <c r="E44" t="str">
-        <v>10043-35-3</v>
+        <v>7664-38-2</v>
       </c>
       <c r="F44" t="str">
-        <v>붕산, Boric Acid</v>
+        <v>인산, H3PO4</v>
       </c>
       <c r="G44" t="str">
-        <v>폐수 / 화학처리</v>
+        <v>세정 / Etch</v>
       </c>
       <c r="H44" t="str">
-        <v>백색 고체</v>
+        <v>무색 액체</v>
       </c>
       <c r="I44" t="str">
-        <v>주의</v>
+        <v>고위험</v>
       </c>
       <c r="J44" t="str">
-        <v>❗ 경고</v>
+        <v>🧪 부식성</v>
       </c>
       <c r="K44" t="str">
-        <v>용액: 약산성 (저농도 자극 가능)</v>
+        <v>85%: 강산성 (부식성)</v>
       </c>
       <c r="L44" t="str">
-        <v>10 mg/m³</v>
+        <v>1 mg/m³</v>
       </c>
       <c r="M44" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>OSHA</v>
       </c>
       <c r="N44" t="str">
-        <v>설정 없음</v>
+        <v>3 mg/m³</v>
       </c>
       <c r="O44" t="str">
-        <v>-</v>
+        <v>ACGIH</v>
       </c>
       <c r="P44" t="str">
-        <v>설정 없음</v>
+        <v>3 mg/m³</v>
       </c>
       <c r="Q44" t="str">
-        <v>-</v>
+        <v>NIOSH</v>
       </c>
       <c r="R44" t="str">
-        <v>설정 없음</v>
+        <v>1000 mg/m³</v>
       </c>
       <c r="S44" t="str">
-        <v>-</v>
+        <v>대표 참고값</v>
       </c>
       <c r="T44" t="str">
-        <v>1.43 g/cm³</v>
+        <v>1.88 g/cm³</v>
       </c>
       <c r="U44" t="str">
         <v>낮음</v>
       </c>
       <c r="V44" t="str">
-        <v>분해</v>
+        <v>158°C</v>
       </c>
       <c r="W44" t="str">
         <v>비가연성</v>
@@ -6286,10 +6286,10 @@
         <v>해당 없음</v>
       </c>
       <c r="AA44" t="str">
-        <v>분진 자극 가능</v>
+        <v>부식성, 산 미스트 가능</v>
       </c>
       <c r="AB44" t="str">
-        <v>수용성</v>
+        <v>희석 시 발열 가능</v>
       </c>
       <c r="AC44" t="str">
         <v>물 세척 가능</v>
@@ -6298,22 +6298,22 @@
         <v>강염기</v>
       </c>
       <c r="AE44" t="str">
-        <v>일반 희석 및 세척</v>
+        <v>알칼리 중화 검토</v>
       </c>
       <c r="AF44" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AG44" t="str">
         <v>가능</v>
       </c>
       <c r="AH44" t="str">
-        <v>일반 중화 불필요</v>
+        <v>중화 가능</v>
       </c>
       <c r="AI44" t="str">
-        <v>보안경, 장갑</v>
+        <v>내산 장갑, 보안면</v>
       </c>
       <c r="AJ44" t="str">
-        <v>분진 흡입 주의</v>
+        <v>산 미스트 흡입 주의</v>
       </c>
       <c r="AK44" t="str">
         <v>N</v>
@@ -6342,49 +6342,49 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B45" t="str">
-        <v>불화수소암모늄</v>
+        <v>초산</v>
       </c>
       <c r="C45" t="str">
-        <v>Ammonium Bifluoride</v>
+        <v>Acetic Acid</v>
       </c>
       <c r="D45" t="str">
-        <v>NH4HF2</v>
+        <v>CH3COOH</v>
       </c>
       <c r="E45" t="str">
-        <v>1341-49-7</v>
+        <v>64-19-7</v>
       </c>
       <c r="F45" t="str">
-        <v>ABF, 불화수소암모늄</v>
+        <v>초산, 빙초산</v>
       </c>
       <c r="G45" t="str">
-        <v>Etch / 세정</v>
+        <v>세정 / 화학공정</v>
       </c>
       <c r="H45" t="str">
-        <v>백색 고체</v>
+        <v>무색 액체</v>
       </c>
       <c r="I45" t="str">
-        <v>매우 위험</v>
+        <v>고위험</v>
       </c>
       <c r="J45" t="str">
-        <v>☠️ 급성독성, 🧪 부식성</v>
+        <v>🔥 인화성, 🧪 부식성</v>
       </c>
       <c r="K45" t="str">
-        <v>용액: 산성 (HF 생성 가능)</v>
+        <v>빙초산: 강산성 (자극성 증기)</v>
       </c>
       <c r="L45" t="str">
-        <v>2.5 mg/m³</v>
+        <v>10 ppm</v>
       </c>
       <c r="M45" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>OSHA</v>
       </c>
       <c r="N45" t="str">
-        <v>5 mg/m³</v>
+        <v>15 ppm</v>
       </c>
       <c r="O45" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>ACGIH</v>
       </c>
       <c r="P45" t="str">
         <v>설정 없음</v>
@@ -6393,46 +6393,46 @@
         <v>-</v>
       </c>
       <c r="R45" t="str">
-        <v>제품 SDS 확인</v>
+        <v>50 ppm</v>
       </c>
       <c r="S45" t="str">
-        <v>제조사 SDS</v>
+        <v>NIOSH</v>
       </c>
       <c r="T45" t="str">
-        <v>1.5 g/cm³</v>
+        <v>1.05 g/cm³</v>
       </c>
       <c r="U45" t="str">
-        <v>낮음</v>
+        <v>11 mmHg</v>
       </c>
       <c r="V45" t="str">
-        <v>분해</v>
+        <v>118°C</v>
       </c>
       <c r="W45" t="str">
-        <v>비가연성</v>
+        <v>39°C</v>
       </c>
       <c r="X45" t="str">
-        <v>해당 없음</v>
+        <v>427°C</v>
       </c>
       <c r="Y45" t="str">
-        <v>해당 없음</v>
+        <v>4%</v>
       </c>
       <c r="Z45" t="str">
-        <v>해당 없음</v>
+        <v>19%</v>
       </c>
       <c r="AA45" t="str">
-        <v>HF 유사 위험성, 피부 침투 독성 가능</v>
+        <v>자극성 증기, 인화성</v>
       </c>
       <c r="AB45" t="str">
-        <v>물에 용해됨</v>
+        <v>물 혼합 가능</v>
       </c>
       <c r="AC45" t="str">
-        <v>대량 물 세척 가능</v>
+        <v>흡착 후 물 세척</v>
       </c>
       <c r="AD45" t="str">
-        <v>강산, 금속</v>
+        <v>산화제</v>
       </c>
       <c r="AE45" t="str">
-        <v>칼슘계 중화 검토</v>
+        <v>알칼리 중화 가능</v>
       </c>
       <c r="AF45" t="str">
         <v>가능</v>
@@ -6441,19 +6441,19 @@
         <v>가능</v>
       </c>
       <c r="AH45" t="str">
-        <v>불소계 중화 검토</v>
+        <v>중화 가능</v>
       </c>
       <c r="AI45" t="str">
-        <v>공기호흡기, 내산 장갑</v>
+        <v>유기증기용 호흡보호구, 보안면</v>
       </c>
       <c r="AJ45" t="str">
-        <v>HF 대응 수준 고려</v>
+        <v>증기 흡입 주의</v>
       </c>
       <c r="AK45" t="str">
         <v>N</v>
       </c>
       <c r="AL45" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM45" t="str">
         <v>N</v>
@@ -6465,7 +6465,7 @@
         <v>N</v>
       </c>
       <c r="AP45" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AQ45" t="str">
         <v>N</v>
@@ -6476,70 +6476,70 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B46" t="str">
-        <v>인산</v>
+        <v>과불화암모늄</v>
       </c>
       <c r="C46" t="str">
-        <v>Phosphoric Acid</v>
+        <v>Ammonium Fluoride Mixture</v>
       </c>
       <c r="D46" t="str">
-        <v>H3PO4</v>
+        <v>NH4F 계열</v>
       </c>
       <c r="E46" t="str">
-        <v>7664-38-2</v>
+        <v>혼합물</v>
       </c>
       <c r="F46" t="str">
-        <v>인산, H3PO4</v>
+        <v>BOE, Buffered Oxide Etch</v>
       </c>
       <c r="G46" t="str">
-        <v>세정 / Etch</v>
+        <v>Etch</v>
       </c>
       <c r="H46" t="str">
-        <v>무색 액체</v>
+        <v>액체</v>
       </c>
       <c r="I46" t="str">
-        <v>고위험</v>
+        <v>매우 위험</v>
       </c>
       <c r="J46" t="str">
-        <v>🧪 부식성</v>
+        <v>☠️ 급성독성, 🧪 부식성</v>
       </c>
       <c r="K46" t="str">
-        <v>85%: 강산성 (부식성)</v>
+        <v>BOE: 산성 (HF 포함 가능)</v>
       </c>
       <c r="L46" t="str">
-        <v>1 mg/m³</v>
+        <v>HF 기준 적용 검토</v>
       </c>
       <c r="M46" t="str">
-        <v>OSHA</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N46" t="str">
-        <v>3 mg/m³</v>
+        <v>HF 기준 적용 검토</v>
       </c>
       <c r="O46" t="str">
-        <v>ACGIH</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="P46" t="str">
-        <v>3 mg/m³</v>
+        <v>HF 기준 적용 검토</v>
       </c>
       <c r="Q46" t="str">
-        <v>NIOSH</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="R46" t="str">
-        <v>1000 mg/m³</v>
+        <v>HF 기준 적용 검토</v>
       </c>
       <c r="S46" t="str">
-        <v>대표 참고값</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="T46" t="str">
-        <v>1.88 g/cm³</v>
+        <v>제품별 상이</v>
       </c>
       <c r="U46" t="str">
-        <v>낮음</v>
+        <v>제품별 상이</v>
       </c>
       <c r="V46" t="str">
-        <v>158°C</v>
+        <v>제품별 상이</v>
       </c>
       <c r="W46" t="str">
         <v>비가연성</v>
@@ -6554,40 +6554,40 @@
         <v>해당 없음</v>
       </c>
       <c r="AA46" t="str">
-        <v>부식성, 산 미스트 가능</v>
+        <v>HF 계열 위험성, 피부 침투 독성 가능</v>
       </c>
       <c r="AB46" t="str">
-        <v>희석 시 발열 가능</v>
+        <v>수용성</v>
       </c>
       <c r="AC46" t="str">
-        <v>물 세척 가능</v>
+        <v>대량 물 세척 가능</v>
       </c>
       <c r="AD46" t="str">
         <v>강염기</v>
       </c>
       <c r="AE46" t="str">
-        <v>알칼리 중화 검토</v>
+        <v>칼슘계 중화 검토</v>
       </c>
       <c r="AF46" t="str">
-        <v>주의</v>
+        <v>가능</v>
       </c>
       <c r="AG46" t="str">
         <v>가능</v>
       </c>
       <c r="AH46" t="str">
-        <v>중화 가능</v>
+        <v>불소계 중화 검토</v>
       </c>
       <c r="AI46" t="str">
-        <v>내산 장갑, 보안면</v>
+        <v>공기호흡기, 내산 장갑</v>
       </c>
       <c r="AJ46" t="str">
-        <v>산 미스트 흡입 주의</v>
+        <v>HF 대응 수준 고려</v>
       </c>
       <c r="AK46" t="str">
         <v>N</v>
       </c>
       <c r="AL46" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM46" t="str">
         <v>N</v>
@@ -6610,25 +6610,25 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B47" t="str">
-        <v>초산</v>
+        <v>크실렌</v>
       </c>
       <c r="C47" t="str">
-        <v>Acetic Acid</v>
+        <v>Xylene</v>
       </c>
       <c r="D47" t="str">
-        <v>CH3COOH</v>
+        <v>C8H10</v>
       </c>
       <c r="E47" t="str">
-        <v>64-19-7</v>
+        <v>1330-20-7</v>
       </c>
       <c r="F47" t="str">
-        <v>초산, 빙초산</v>
+        <v>Xylene, 자일렌</v>
       </c>
       <c r="G47" t="str">
-        <v>세정 / 화학공정</v>
+        <v>용제 / 세정</v>
       </c>
       <c r="H47" t="str">
         <v>무색 액체</v>
@@ -6637,19 +6637,19 @@
         <v>고위험</v>
       </c>
       <c r="J47" t="str">
-        <v>🔥 인화성, 🧪 부식성</v>
+        <v>🔥 인화성, ❗ 경고</v>
       </c>
       <c r="K47" t="str">
-        <v>빙초산: 강산성 (자극성 증기)</v>
+        <v>원액: 중성 (유기용제)</v>
       </c>
       <c r="L47" t="str">
-        <v>10 ppm</v>
+        <v>100 ppm</v>
       </c>
       <c r="M47" t="str">
         <v>OSHA</v>
       </c>
       <c r="N47" t="str">
-        <v>15 ppm</v>
+        <v>150 ppm</v>
       </c>
       <c r="O47" t="str">
         <v>ACGIH</v>
@@ -6661,61 +6661,61 @@
         <v>-</v>
       </c>
       <c r="R47" t="str">
-        <v>50 ppm</v>
+        <v>900 ppm</v>
       </c>
       <c r="S47" t="str">
         <v>NIOSH</v>
       </c>
       <c r="T47" t="str">
-        <v>1.05 g/cm³</v>
+        <v>0.86 g/cm³</v>
       </c>
       <c r="U47" t="str">
-        <v>11 mmHg</v>
+        <v>8 mmHg</v>
       </c>
       <c r="V47" t="str">
-        <v>118°C</v>
+        <v>138°C</v>
       </c>
       <c r="W47" t="str">
-        <v>39°C</v>
+        <v>27°C</v>
       </c>
       <c r="X47" t="str">
-        <v>427°C</v>
+        <v>465°C</v>
       </c>
       <c r="Y47" t="str">
-        <v>4%</v>
+        <v>1%</v>
       </c>
       <c r="Z47" t="str">
-        <v>19%</v>
+        <v>7%</v>
       </c>
       <c r="AA47" t="str">
-        <v>자극성 증기, 인화성</v>
+        <v>인화성, 중추신경계 영향 가능</v>
       </c>
       <c r="AB47" t="str">
-        <v>물 혼합 가능</v>
+        <v>물에 잘 안녹음</v>
       </c>
       <c r="AC47" t="str">
-        <v>흡착 후 물 세척</v>
+        <v>흡착·환기 우선</v>
       </c>
       <c r="AD47" t="str">
-        <v>산화제</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE47" t="str">
-        <v>알칼리 중화 가능</v>
+        <v>흡착·회수 우선</v>
       </c>
       <c r="AF47" t="str">
         <v>가능</v>
       </c>
       <c r="AG47" t="str">
-        <v>가능</v>
+        <v>확산 가능성 고려</v>
       </c>
       <c r="AH47" t="str">
-        <v>중화 가능</v>
+        <v>일반 중화 대상 아님</v>
       </c>
       <c r="AI47" t="str">
-        <v>유기증기용 호흡보호구, 보안면</v>
+        <v>유기증기용 호흡보호구, 방염 보호구</v>
       </c>
       <c r="AJ47" t="str">
-        <v>증기 흡입 주의</v>
+        <v>정전기 점화 주의</v>
       </c>
       <c r="AK47" t="str">
         <v>N</v>
@@ -6744,28 +6744,28 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" t="str">
-        <v>과불화암모늄</v>
+        <v>황화나트륨</v>
       </c>
       <c r="C48" t="str">
-        <v>Ammonium Fluoride Mixture</v>
+        <v>Sodium Sulfide</v>
       </c>
       <c r="D48" t="str">
-        <v>NH4F 계열</v>
+        <v>Na2S</v>
       </c>
       <c r="E48" t="str">
-        <v>혼합물</v>
+        <v>1313-82-2</v>
       </c>
       <c r="F48" t="str">
-        <v>BOE, Buffered Oxide Etch</v>
+        <v>Na2S, 황화소다</v>
       </c>
       <c r="G48" t="str">
-        <v>Etch</v>
+        <v>폐수 / 중금속 처리</v>
       </c>
       <c r="H48" t="str">
-        <v>액체</v>
+        <v>황색 고체</v>
       </c>
       <c r="I48" t="str">
         <v>매우 위험</v>
@@ -6774,40 +6774,40 @@
         <v>☠️ 급성독성, 🧪 부식성</v>
       </c>
       <c r="K48" t="str">
-        <v>BOE: 산성 (HF 포함 가능)</v>
+        <v>용액: 강염기성 (산 접촉 시 H2S 발생 가능)</v>
       </c>
       <c r="L48" t="str">
-        <v>HF 기준 적용 검토</v>
+        <v>H2S 기준 적용 검토</v>
       </c>
       <c r="M48" t="str">
         <v>대표 SDS 참고값</v>
       </c>
       <c r="N48" t="str">
-        <v>HF 기준 적용 검토</v>
+        <v>H2S 기준 적용 검토</v>
       </c>
       <c r="O48" t="str">
         <v>대표 SDS 참고값</v>
       </c>
       <c r="P48" t="str">
-        <v>HF 기준 적용 검토</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q48" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>-</v>
       </c>
       <c r="R48" t="str">
-        <v>HF 기준 적용 검토</v>
+        <v>H2S 기준 검토</v>
       </c>
       <c r="S48" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>NIOSH 참고</v>
       </c>
       <c r="T48" t="str">
-        <v>제품별 상이</v>
+        <v>1.86 g/cm³</v>
       </c>
       <c r="U48" t="str">
-        <v>제품별 상이</v>
+        <v>낮음</v>
       </c>
       <c r="V48" t="str">
-        <v>제품별 상이</v>
+        <v>분해</v>
       </c>
       <c r="W48" t="str">
         <v>비가연성</v>
@@ -6816,40 +6816,40 @@
         <v>해당 없음</v>
       </c>
       <c r="Y48" t="str">
-        <v>해당 없음</v>
+        <v>H2S 발생 시 적용</v>
       </c>
       <c r="Z48" t="str">
-        <v>해당 없음</v>
+        <v>H2S 발생 시 적용</v>
       </c>
       <c r="AA48" t="str">
-        <v>HF 계열 위험성, 피부 침투 독성 가능</v>
+        <v>산 접촉 시 H2S 발생 가능, 부식성, 중금속 침전제</v>
       </c>
       <c r="AB48" t="str">
-        <v>수용성</v>
+        <v>산 혼합 시 황화수소 발생 가능</v>
       </c>
       <c r="AC48" t="str">
-        <v>대량 물 세척 가능</v>
+        <v>환기 및 산 분리 우선</v>
       </c>
       <c r="AD48" t="str">
-        <v>강염기</v>
+        <v>산, 산화제</v>
       </c>
       <c r="AE48" t="str">
-        <v>칼슘계 중화 검토</v>
+        <v>산 접촉 차단 우선</v>
       </c>
       <c r="AF48" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AG48" t="str">
-        <v>가능</v>
+        <v>가능하나 H2S 발생 주의</v>
       </c>
       <c r="AH48" t="str">
-        <v>불소계 중화 검토</v>
+        <v>산 혼합 금지</v>
       </c>
       <c r="AI48" t="str">
-        <v>공기호흡기, 내산 장갑</v>
+        <v>공기호흡기, 내화학 장갑</v>
       </c>
       <c r="AJ48" t="str">
-        <v>HF 대응 수준 고려</v>
+        <v>산 접촉 절대 주의</v>
       </c>
       <c r="AK48" t="str">
         <v>N</v>
@@ -6878,49 +6878,49 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B49" t="str">
-        <v>크실렌</v>
+        <v>황산제일철</v>
       </c>
       <c r="C49" t="str">
-        <v>Xylene</v>
+        <v>Ferrous Sulfate</v>
       </c>
       <c r="D49" t="str">
-        <v>C8H10</v>
+        <v>FeSO4</v>
       </c>
       <c r="E49" t="str">
-        <v>1330-20-7</v>
+        <v>7720-78-7</v>
       </c>
       <c r="F49" t="str">
-        <v>Xylene, 자일렌</v>
+        <v>FeSO4, 황산철</v>
       </c>
       <c r="G49" t="str">
-        <v>용제 / 세정</v>
+        <v>폐수 / Cr 환원</v>
       </c>
       <c r="H49" t="str">
-        <v>무색 액체</v>
+        <v>녹색 고체</v>
       </c>
       <c r="I49" t="str">
-        <v>고위험</v>
+        <v>주의</v>
       </c>
       <c r="J49" t="str">
-        <v>🔥 인화성, ❗ 경고</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K49" t="str">
-        <v>원액: 중성 (유기용제)</v>
+        <v>용액: 약산성 (환원제 역할)</v>
       </c>
       <c r="L49" t="str">
-        <v>100 ppm</v>
+        <v>1 mg/m³</v>
       </c>
       <c r="M49" t="str">
-        <v>OSHA</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N49" t="str">
-        <v>150 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="O49" t="str">
-        <v>ACGIH</v>
+        <v>-</v>
       </c>
       <c r="P49" t="str">
         <v>설정 없음</v>
@@ -6929,61 +6929,61 @@
         <v>-</v>
       </c>
       <c r="R49" t="str">
-        <v>900 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="S49" t="str">
-        <v>NIOSH</v>
+        <v>-</v>
       </c>
       <c r="T49" t="str">
-        <v>0.86 g/cm³</v>
+        <v>1.9 g/cm³</v>
       </c>
       <c r="U49" t="str">
-        <v>8 mmHg</v>
+        <v>낮음</v>
       </c>
       <c r="V49" t="str">
-        <v>138°C</v>
+        <v>분해</v>
       </c>
       <c r="W49" t="str">
-        <v>27°C</v>
+        <v>비가연성</v>
       </c>
       <c r="X49" t="str">
-        <v>465°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y49" t="str">
-        <v>1%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z49" t="str">
-        <v>7%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA49" t="str">
-        <v>인화성, 중추신경계 영향 가능</v>
+        <v>분진 자극 가능, 폐수 환원제</v>
       </c>
       <c r="AB49" t="str">
-        <v>물에 잘 안녹음</v>
+        <v>수용성</v>
       </c>
       <c r="AC49" t="str">
-        <v>흡착·환기 우선</v>
+        <v>물 세척 가능</v>
       </c>
       <c r="AD49" t="str">
-        <v>산화제, 점화원</v>
+        <v>강산화제</v>
       </c>
       <c r="AE49" t="str">
-        <v>흡착·회수 우선</v>
+        <v>일반 희석 및 세척</v>
       </c>
       <c r="AF49" t="str">
         <v>가능</v>
       </c>
       <c r="AG49" t="str">
-        <v>확산 가능성 고려</v>
+        <v>가능</v>
       </c>
       <c r="AH49" t="str">
-        <v>일반 중화 대상 아님</v>
+        <v>일반 중화 불필요</v>
       </c>
       <c r="AI49" t="str">
-        <v>유기증기용 호흡보호구, 방염 보호구</v>
+        <v>보안경, 장갑</v>
       </c>
       <c r="AJ49" t="str">
-        <v>정전기 점화 주의</v>
+        <v>분진 흡입 주의</v>
       </c>
       <c r="AK49" t="str">
         <v>N</v>
@@ -7012,46 +7012,46 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" t="str">
-        <v>황화나트륨</v>
+        <v>염화제이철</v>
       </c>
       <c r="C50" t="str">
-        <v>Sodium Sulfide</v>
+        <v>Ferric Chloride</v>
       </c>
       <c r="D50" t="str">
-        <v>Na2S</v>
+        <v>FeCl3</v>
       </c>
       <c r="E50" t="str">
-        <v>1313-82-2</v>
+        <v>7705-08-0</v>
       </c>
       <c r="F50" t="str">
-        <v>Na2S, 황화소다</v>
+        <v>FeCl3, 염화철</v>
       </c>
       <c r="G50" t="str">
-        <v>폐수 / 중금속 처리</v>
+        <v>폐수 / 응집</v>
       </c>
       <c r="H50" t="str">
-        <v>황색 고체</v>
+        <v>갈색 액체</v>
       </c>
       <c r="I50" t="str">
-        <v>매우 위험</v>
+        <v>고위험</v>
       </c>
       <c r="J50" t="str">
-        <v>☠️ 급성독성, 🧪 부식성</v>
+        <v>🧪 부식성</v>
       </c>
       <c r="K50" t="str">
-        <v>용액: 강염기성 (산 접촉 시 H2S 발생 가능)</v>
+        <v>원액: 강산성 (부식성)</v>
       </c>
       <c r="L50" t="str">
-        <v>H2S 기준 적용 검토</v>
+        <v>1 mg/m³</v>
       </c>
       <c r="M50" t="str">
         <v>대표 SDS 참고값</v>
       </c>
       <c r="N50" t="str">
-        <v>H2S 기준 적용 검토</v>
+        <v>2 mg/m³</v>
       </c>
       <c r="O50" t="str">
         <v>대표 SDS 참고값</v>
@@ -7063,13 +7063,13 @@
         <v>-</v>
       </c>
       <c r="R50" t="str">
-        <v>H2S 기준 검토</v>
+        <v>설정 없음</v>
       </c>
       <c r="S50" t="str">
-        <v>NIOSH 참고</v>
+        <v>-</v>
       </c>
       <c r="T50" t="str">
-        <v>1.86 g/cm³</v>
+        <v>1.4 g/cm³</v>
       </c>
       <c r="U50" t="str">
         <v>낮음</v>
@@ -7084,46 +7084,46 @@
         <v>해당 없음</v>
       </c>
       <c r="Y50" t="str">
-        <v>H2S 발생 시 적용</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z50" t="str">
-        <v>H2S 발생 시 적용</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA50" t="str">
-        <v>산 접촉 시 H2S 발생 가능, 부식성, 중금속 침전제</v>
+        <v>강한 부식성, 응집제</v>
       </c>
       <c r="AB50" t="str">
-        <v>산 혼합 시 황화수소 발생 가능</v>
+        <v>물과 혼합 시 산성</v>
       </c>
       <c r="AC50" t="str">
-        <v>환기 및 산 분리 우선</v>
+        <v>대량 물 세척 가능</v>
       </c>
       <c r="AD50" t="str">
-        <v>산, 산화제</v>
+        <v>강염기, 금속</v>
       </c>
       <c r="AE50" t="str">
-        <v>산 접촉 차단 우선</v>
+        <v>알칼리 중화 가능</v>
       </c>
       <c r="AF50" t="str">
-        <v>주의</v>
+        <v>가능</v>
       </c>
       <c r="AG50" t="str">
-        <v>가능하나 H2S 발생 주의</v>
+        <v>가능</v>
       </c>
       <c r="AH50" t="str">
-        <v>산 혼합 금지</v>
+        <v>중화 가능</v>
       </c>
       <c r="AI50" t="str">
-        <v>공기호흡기, 내화학 장갑</v>
+        <v>내산 장갑, 보안면</v>
       </c>
       <c r="AJ50" t="str">
-        <v>산 접촉 절대 주의</v>
+        <v>금속 부식 가능</v>
       </c>
       <c r="AK50" t="str">
         <v>N</v>
       </c>
       <c r="AL50" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM50" t="str">
         <v>N</v>
@@ -7146,43 +7146,43 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B51" t="str">
-        <v>황산제일철</v>
+        <v>수산화칼슘</v>
       </c>
       <c r="C51" t="str">
-        <v>Ferrous Sulfate</v>
+        <v>Calcium Hydroxide</v>
       </c>
       <c r="D51" t="str">
-        <v>FeSO4</v>
+        <v>Ca(OH)2</v>
       </c>
       <c r="E51" t="str">
-        <v>7720-78-7</v>
+        <v>1305-62-0</v>
       </c>
       <c r="F51" t="str">
-        <v>FeSO4, 황산철</v>
+        <v>소석회, CaOH</v>
       </c>
       <c r="G51" t="str">
-        <v>폐수 / Cr 환원</v>
+        <v>폐수 / 중화</v>
       </c>
       <c r="H51" t="str">
-        <v>녹색 고체</v>
+        <v>백색 분말</v>
       </c>
       <c r="I51" t="str">
-        <v>주의</v>
+        <v>고위험</v>
       </c>
       <c r="J51" t="str">
-        <v>❗ 경고</v>
+        <v>🧪 부식성</v>
       </c>
       <c r="K51" t="str">
-        <v>용액: 약산성 (환원제 역할)</v>
+        <v>포화용액: 강염기성 (중화제)</v>
       </c>
       <c r="L51" t="str">
-        <v>1 mg/m³</v>
+        <v>5 mg/m³</v>
       </c>
       <c r="M51" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>OSHA 대표값</v>
       </c>
       <c r="N51" t="str">
         <v>설정 없음</v>
@@ -7191,10 +7191,10 @@
         <v>-</v>
       </c>
       <c r="P51" t="str">
-        <v>설정 없음</v>
+        <v>15 mg/m³</v>
       </c>
       <c r="Q51" t="str">
-        <v>-</v>
+        <v>대표 참고값</v>
       </c>
       <c r="R51" t="str">
         <v>설정 없음</v>
@@ -7203,7 +7203,7 @@
         <v>-</v>
       </c>
       <c r="T51" t="str">
-        <v>1.9 g/cm³</v>
+        <v>2.2 g/cm³</v>
       </c>
       <c r="U51" t="str">
         <v>낮음</v>
@@ -7224,31 +7224,31 @@
         <v>해당 없음</v>
       </c>
       <c r="AA51" t="str">
-        <v>분진 자극 가능, 폐수 환원제</v>
+        <v>강염기성, 분진 자극</v>
       </c>
       <c r="AB51" t="str">
-        <v>수용성</v>
+        <v>물 혼합 시 발열 가능</v>
       </c>
       <c r="AC51" t="str">
         <v>물 세척 가능</v>
       </c>
       <c r="AD51" t="str">
-        <v>강산화제</v>
+        <v>산</v>
       </c>
       <c r="AE51" t="str">
-        <v>일반 희석 및 세척</v>
+        <v>산성 폐수 중화</v>
       </c>
       <c r="AF51" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AG51" t="str">
         <v>가능</v>
       </c>
       <c r="AH51" t="str">
-        <v>일반 중화 불필요</v>
+        <v>대표 중화제</v>
       </c>
       <c r="AI51" t="str">
-        <v>보안경, 장갑</v>
+        <v>방진마스크, 보안경</v>
       </c>
       <c r="AJ51" t="str">
         <v>분진 흡입 주의</v>
@@ -7280,49 +7280,49 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" t="str">
-        <v>염화제이철</v>
+        <v>EDTA</v>
       </c>
       <c r="C52" t="str">
-        <v>Ferric Chloride</v>
+        <v>Ethylenediaminetetraacetic Acid</v>
       </c>
       <c r="D52" t="str">
-        <v>FeCl3</v>
+        <v>C10H16N2O8</v>
       </c>
       <c r="E52" t="str">
-        <v>7705-08-0</v>
+        <v>60-00-4</v>
       </c>
       <c r="F52" t="str">
-        <v>FeCl3, 염화철</v>
+        <v>EDTA, 킬레이트제</v>
       </c>
       <c r="G52" t="str">
-        <v>폐수 / 응집</v>
+        <v>수처리 / 금속 제거</v>
       </c>
       <c r="H52" t="str">
-        <v>갈색 액체</v>
+        <v>백색 분말</v>
       </c>
       <c r="I52" t="str">
-        <v>고위험</v>
+        <v>주의</v>
       </c>
       <c r="J52" t="str">
-        <v>🧪 부식성</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K52" t="str">
-        <v>원액: 강산성 (부식성)</v>
+        <v>용액: 약산성 (금속 킬레이트)</v>
       </c>
       <c r="L52" t="str">
-        <v>1 mg/m³</v>
+        <v>설정 없음</v>
       </c>
       <c r="M52" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>-</v>
       </c>
       <c r="N52" t="str">
-        <v>2 mg/m³</v>
+        <v>설정 없음</v>
       </c>
       <c r="O52" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>-</v>
       </c>
       <c r="P52" t="str">
         <v>설정 없음</v>
@@ -7337,7 +7337,7 @@
         <v>-</v>
       </c>
       <c r="T52" t="str">
-        <v>1.4 g/cm³</v>
+        <v>0.8 g/cm³</v>
       </c>
       <c r="U52" t="str">
         <v>낮음</v>
@@ -7358,19 +7358,19 @@
         <v>해당 없음</v>
       </c>
       <c r="AA52" t="str">
-        <v>강한 부식성, 응집제</v>
+        <v>금속 이온 킬레이트, 분진 자극 가능</v>
       </c>
       <c r="AB52" t="str">
-        <v>물과 혼합 시 산성</v>
+        <v>수용성</v>
       </c>
       <c r="AC52" t="str">
-        <v>대량 물 세척 가능</v>
+        <v>물 세척 가능</v>
       </c>
       <c r="AD52" t="str">
-        <v>강염기, 금속</v>
+        <v>강산화제</v>
       </c>
       <c r="AE52" t="str">
-        <v>알칼리 중화 가능</v>
+        <v>일반 희석 및 세척</v>
       </c>
       <c r="AF52" t="str">
         <v>가능</v>
@@ -7379,13 +7379,13 @@
         <v>가능</v>
       </c>
       <c r="AH52" t="str">
-        <v>중화 가능</v>
+        <v>일반 중화 불필요</v>
       </c>
       <c r="AI52" t="str">
-        <v>내산 장갑, 보안면</v>
+        <v>보안경, 장갑</v>
       </c>
       <c r="AJ52" t="str">
-        <v>금속 부식 가능</v>
+        <v>분진 흡입 주의</v>
       </c>
       <c r="AK52" t="str">
         <v>N</v>
@@ -7414,40 +7414,40 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" t="str">
-        <v>수산화칼슘</v>
+        <v>과망간산칼륨</v>
       </c>
       <c r="C53" t="str">
-        <v>Calcium Hydroxide</v>
+        <v>Potassium Permanganate</v>
       </c>
       <c r="D53" t="str">
-        <v>Ca(OH)2</v>
+        <v>KMnO4</v>
       </c>
       <c r="E53" t="str">
-        <v>1305-62-0</v>
+        <v>7722-64-7</v>
       </c>
       <c r="F53" t="str">
-        <v>소석회, CaOH</v>
+        <v>KMnO4</v>
       </c>
       <c r="G53" t="str">
-        <v>폐수 / 중화</v>
+        <v>Scrubber / 산화처리</v>
       </c>
       <c r="H53" t="str">
-        <v>백색 분말</v>
+        <v>보라색 고체</v>
       </c>
       <c r="I53" t="str">
         <v>고위험</v>
       </c>
       <c r="J53" t="str">
-        <v>🧪 부식성</v>
+        <v>⭕ 산화성, ❗ 경고</v>
       </c>
       <c r="K53" t="str">
-        <v>포화용액: 강염기성 (중화제)</v>
+        <v>용액: 중성 부근 (강산화성)</v>
       </c>
       <c r="L53" t="str">
-        <v>5 mg/m³</v>
+        <v>0.2 mg/m³</v>
       </c>
       <c r="M53" t="str">
         <v>OSHA 대표값</v>
@@ -7459,10 +7459,10 @@
         <v>-</v>
       </c>
       <c r="P53" t="str">
-        <v>15 mg/m³</v>
+        <v>0.2 mg/m³</v>
       </c>
       <c r="Q53" t="str">
-        <v>대표 참고값</v>
+        <v>NIOSH 참고</v>
       </c>
       <c r="R53" t="str">
         <v>설정 없음</v>
@@ -7471,7 +7471,7 @@
         <v>-</v>
       </c>
       <c r="T53" t="str">
-        <v>2.2 g/cm³</v>
+        <v>2.7 g/cm³</v>
       </c>
       <c r="U53" t="str">
         <v>낮음</v>
@@ -7480,7 +7480,7 @@
         <v>분해</v>
       </c>
       <c r="W53" t="str">
-        <v>비가연성</v>
+        <v>산화성</v>
       </c>
       <c r="X53" t="str">
         <v>해당 없음</v>
@@ -7492,34 +7492,34 @@
         <v>해당 없음</v>
       </c>
       <c r="AA53" t="str">
-        <v>강염기성, 분진 자극</v>
+        <v>강산화성, 유기물 반응 가능</v>
       </c>
       <c r="AB53" t="str">
-        <v>물 혼합 시 발열 가능</v>
+        <v>수용성</v>
       </c>
       <c r="AC53" t="str">
-        <v>물 세척 가능</v>
+        <v>오염 제거 후 세척</v>
       </c>
       <c r="AD53" t="str">
-        <v>산</v>
+        <v>유기물, 환원제</v>
       </c>
       <c r="AE53" t="str">
-        <v>산성 폐수 중화</v>
+        <v>환원 처리 검토</v>
       </c>
       <c r="AF53" t="str">
-        <v>주의</v>
+        <v>가능</v>
       </c>
       <c r="AG53" t="str">
         <v>가능</v>
       </c>
       <c r="AH53" t="str">
-        <v>대표 중화제</v>
+        <v>산화성 관리 필요</v>
       </c>
       <c r="AI53" t="str">
-        <v>방진마스크, 보안경</v>
+        <v>보안면, 내화학 장갑</v>
       </c>
       <c r="AJ53" t="str">
-        <v>분진 흡입 주의</v>
+        <v>유기물 접촉 주의</v>
       </c>
       <c r="AK53" t="str">
         <v>N</v>
@@ -7528,13 +7528,13 @@
         <v>N</v>
       </c>
       <c r="AM53" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN53" t="str">
         <v>Y</v>
       </c>
       <c r="AO53" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP53" t="str">
         <v>N</v>
@@ -7548,25 +7548,25 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" t="str">
-        <v>EDTA</v>
+        <v>차아황산나트륨</v>
       </c>
       <c r="C54" t="str">
-        <v>Ethylenediaminetetraacetic Acid</v>
+        <v>Sodium Bisulfite</v>
       </c>
       <c r="D54" t="str">
-        <v>C10H16N2O8</v>
+        <v>NaHSO3</v>
       </c>
       <c r="E54" t="str">
-        <v>60-00-4</v>
+        <v>7631-90-5</v>
       </c>
       <c r="F54" t="str">
-        <v>EDTA, 킬레이트제</v>
+        <v>중아황산나트륨, NaHSO3</v>
       </c>
       <c r="G54" t="str">
-        <v>수처리 / 금속 제거</v>
+        <v>UPW / 잔류염소 제거</v>
       </c>
       <c r="H54" t="str">
         <v>백색 분말</v>
@@ -7578,13 +7578,13 @@
         <v>❗ 경고</v>
       </c>
       <c r="K54" t="str">
-        <v>용액: 약산성 (금속 킬레이트)</v>
+        <v>용액: 약산성 (환원제)</v>
       </c>
       <c r="L54" t="str">
-        <v>설정 없음</v>
+        <v>5 mg/m³</v>
       </c>
       <c r="M54" t="str">
-        <v>-</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N54" t="str">
         <v>설정 없음</v>
@@ -7605,7 +7605,7 @@
         <v>-</v>
       </c>
       <c r="T54" t="str">
-        <v>0.8 g/cm³</v>
+        <v>1.5 g/cm³</v>
       </c>
       <c r="U54" t="str">
         <v>낮음</v>
@@ -7626,19 +7626,19 @@
         <v>해당 없음</v>
       </c>
       <c r="AA54" t="str">
-        <v>금속 이온 킬레이트, 분진 자극 가능</v>
+        <v>SO2 발생 가능, 환원제</v>
       </c>
       <c r="AB54" t="str">
-        <v>수용성</v>
+        <v>산 접촉 시 SO2 발생 가능</v>
       </c>
       <c r="AC54" t="str">
-        <v>물 세척 가능</v>
+        <v>환기 및 세척</v>
       </c>
       <c r="AD54" t="str">
-        <v>강산화제</v>
+        <v>산화제, 산</v>
       </c>
       <c r="AE54" t="str">
-        <v>일반 희석 및 세척</v>
+        <v>산 접촉 차단</v>
       </c>
       <c r="AF54" t="str">
         <v>가능</v>
@@ -7653,7 +7653,7 @@
         <v>보안경, 장갑</v>
       </c>
       <c r="AJ54" t="str">
-        <v>분진 흡입 주의</v>
+        <v>산 혼합 시 SO2 발생 가능</v>
       </c>
       <c r="AK54" t="str">
         <v>N</v>
@@ -7682,43 +7682,43 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" t="str">
-        <v>과망간산칼륨</v>
+        <v>활성탄 슬러리</v>
       </c>
       <c r="C55" t="str">
-        <v>Potassium Permanganate</v>
+        <v>Activated Carbon Slurry</v>
       </c>
       <c r="D55" t="str">
-        <v>KMnO4</v>
+        <v>혼합물</v>
       </c>
       <c r="E55" t="str">
-        <v>7722-64-7</v>
+        <v>혼합물</v>
       </c>
       <c r="F55" t="str">
-        <v>KMnO4</v>
+        <v>활성탄</v>
       </c>
       <c r="G55" t="str">
-        <v>Scrubber / 산화처리</v>
+        <v>VOC 제거 / Scrubber</v>
       </c>
       <c r="H55" t="str">
-        <v>보라색 고체</v>
+        <v>검정 슬러리</v>
       </c>
       <c r="I55" t="str">
-        <v>고위험</v>
+        <v>주의</v>
       </c>
       <c r="J55" t="str">
-        <v>⭕ 산화성, ❗ 경고</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K55" t="str">
-        <v>용액: 중성 부근 (강산화성)</v>
+        <v>슬러리: 중성 부근 (흡착제)</v>
       </c>
       <c r="L55" t="str">
-        <v>0.2 mg/m³</v>
+        <v>분진 기준 적용</v>
       </c>
       <c r="M55" t="str">
-        <v>OSHA 대표값</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N55" t="str">
         <v>설정 없음</v>
@@ -7727,10 +7727,10 @@
         <v>-</v>
       </c>
       <c r="P55" t="str">
-        <v>0.2 mg/m³</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q55" t="str">
-        <v>NIOSH 참고</v>
+        <v>-</v>
       </c>
       <c r="R55" t="str">
         <v>설정 없음</v>
@@ -7739,40 +7739,40 @@
         <v>-</v>
       </c>
       <c r="T55" t="str">
-        <v>2.7 g/cm³</v>
+        <v>혼합물</v>
       </c>
       <c r="U55" t="str">
         <v>낮음</v>
       </c>
       <c r="V55" t="str">
-        <v>분해</v>
+        <v>해당 없음</v>
       </c>
       <c r="W55" t="str">
-        <v>산화성</v>
+        <v>분진 주의</v>
       </c>
       <c r="X55" t="str">
-        <v>해당 없음</v>
+        <v>제품별 상이</v>
       </c>
       <c r="Y55" t="str">
-        <v>해당 없음</v>
+        <v>분진 조건</v>
       </c>
       <c r="Z55" t="str">
-        <v>해당 없음</v>
+        <v>분진 조건</v>
       </c>
       <c r="AA55" t="str">
-        <v>강산화성, 유기물 반응 가능</v>
+        <v>분진 폭발 가능, 흡착 포화 시 발열 가능</v>
       </c>
       <c r="AB55" t="str">
-        <v>수용성</v>
+        <v>슬러리 형태 사용</v>
       </c>
       <c r="AC55" t="str">
-        <v>오염 제거 후 세척</v>
+        <v>흡착 및 회수</v>
       </c>
       <c r="AD55" t="str">
-        <v>유기물, 환원제</v>
+        <v>강산화제</v>
       </c>
       <c r="AE55" t="str">
-        <v>환원 처리 검토</v>
+        <v>회수 및 폐기</v>
       </c>
       <c r="AF55" t="str">
         <v>가능</v>
@@ -7781,13 +7781,13 @@
         <v>가능</v>
       </c>
       <c r="AH55" t="str">
-        <v>산화성 관리 필요</v>
+        <v>일반 중화 불필요</v>
       </c>
       <c r="AI55" t="str">
-        <v>보안면, 내화학 장갑</v>
+        <v>방진마스크, 보안경</v>
       </c>
       <c r="AJ55" t="str">
-        <v>유기물 접촉 주의</v>
+        <v>건조 분진 주의</v>
       </c>
       <c r="AK55" t="str">
         <v>N</v>
@@ -7796,13 +7796,13 @@
         <v>N</v>
       </c>
       <c r="AM55" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AN55" t="str">
         <v>Y</v>
       </c>
       <c r="AO55" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AP55" t="str">
         <v>N</v>
@@ -7816,28 +7816,28 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B56" t="str">
-        <v>차아황산나트륨</v>
+        <v>리튬브로마이드</v>
       </c>
       <c r="C56" t="str">
-        <v>Sodium Bisulfite</v>
+        <v>Lithium Bromide</v>
       </c>
       <c r="D56" t="str">
-        <v>NaHSO3</v>
+        <v>LiBr</v>
       </c>
       <c r="E56" t="str">
-        <v>7631-90-5</v>
+        <v>7550-35-8</v>
       </c>
       <c r="F56" t="str">
-        <v>중아황산나트륨, NaHSO3</v>
+        <v>LiBr</v>
       </c>
       <c r="G56" t="str">
-        <v>UPW / 잔류염소 제거</v>
+        <v>흡수식 냉동기</v>
       </c>
       <c r="H56" t="str">
-        <v>백색 분말</v>
+        <v>무색 용액</v>
       </c>
       <c r="I56" t="str">
         <v>주의</v>
@@ -7846,13 +7846,13 @@
         <v>❗ 경고</v>
       </c>
       <c r="K56" t="str">
-        <v>용액: 약산성 (환원제)</v>
+        <v>용액: 중성 부근 (흡수식 냉동기 사용)</v>
       </c>
       <c r="L56" t="str">
-        <v>5 mg/m³</v>
+        <v>설정 없음</v>
       </c>
       <c r="M56" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>-</v>
       </c>
       <c r="N56" t="str">
         <v>설정 없음</v>
@@ -7873,13 +7873,13 @@
         <v>-</v>
       </c>
       <c r="T56" t="str">
-        <v>1.5 g/cm³</v>
+        <v>1.6 g/cm³</v>
       </c>
       <c r="U56" t="str">
         <v>낮음</v>
       </c>
       <c r="V56" t="str">
-        <v>분해</v>
+        <v>1265°C</v>
       </c>
       <c r="W56" t="str">
         <v>비가연성</v>
@@ -7894,19 +7894,19 @@
         <v>해당 없음</v>
       </c>
       <c r="AA56" t="str">
-        <v>SO2 발생 가능, 환원제</v>
+        <v>흡수식 냉동기 사용, 누출 시 미끄럼 위험</v>
       </c>
       <c r="AB56" t="str">
-        <v>산 접촉 시 SO2 발생 가능</v>
+        <v>수용성</v>
       </c>
       <c r="AC56" t="str">
-        <v>환기 및 세척</v>
+        <v>물 세척 가능</v>
       </c>
       <c r="AD56" t="str">
-        <v>산화제, 산</v>
+        <v>강산화제</v>
       </c>
       <c r="AE56" t="str">
-        <v>산 접촉 차단</v>
+        <v>희석 및 회수</v>
       </c>
       <c r="AF56" t="str">
         <v>가능</v>
@@ -7921,7 +7921,7 @@
         <v>보안경, 장갑</v>
       </c>
       <c r="AJ56" t="str">
-        <v>산 혼합 시 SO2 발생 가능</v>
+        <v>대량 누출 시 미끄럼 위험</v>
       </c>
       <c r="AK56" t="str">
         <v>N</v>
@@ -7950,40 +7950,40 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B57" t="str">
-        <v>활성탄 슬러리</v>
+        <v>R-123</v>
       </c>
       <c r="C57" t="str">
-        <v>Activated Carbon Slurry</v>
+        <v>HCFC-123</v>
       </c>
       <c r="D57" t="str">
-        <v>혼합물</v>
+        <v>C2HCl2F3</v>
       </c>
       <c r="E57" t="str">
-        <v>혼합물</v>
+        <v>306-83-2</v>
       </c>
       <c r="F57" t="str">
-        <v>활성탄</v>
+        <v>R123, HCFC-123</v>
       </c>
       <c r="G57" t="str">
-        <v>VOC 제거 / Scrubber</v>
+        <v>터보냉동기</v>
       </c>
       <c r="H57" t="str">
-        <v>검정 슬러리</v>
+        <v>무색 액체</v>
       </c>
       <c r="I57" t="str">
         <v>주의</v>
       </c>
       <c r="J57" t="str">
-        <v>❗ 경고</v>
+        <v>🧯 가스실린더</v>
       </c>
       <c r="K57" t="str">
-        <v>슬러리: 중성 부근 (흡착제)</v>
+        <v>냉매: 해당 없음 (밀폐공간 질식 위험)</v>
       </c>
       <c r="L57" t="str">
-        <v>분진 기준 적용</v>
+        <v>50 ppm</v>
       </c>
       <c r="M57" t="str">
         <v>대표 SDS 참고값</v>
@@ -8001,67 +8001,67 @@
         <v>-</v>
       </c>
       <c r="R57" t="str">
-        <v>설정 없음</v>
+        <v>1000 ppm</v>
       </c>
       <c r="S57" t="str">
-        <v>-</v>
+        <v>대표 참고값</v>
       </c>
       <c r="T57" t="str">
-        <v>혼합물</v>
+        <v>1.46 g/cm³</v>
       </c>
       <c r="U57" t="str">
-        <v>낮음</v>
+        <v>높음</v>
       </c>
       <c r="V57" t="str">
-        <v>해당 없음</v>
+        <v>27°C</v>
       </c>
       <c r="W57" t="str">
-        <v>분진 주의</v>
+        <v>비가연성</v>
       </c>
       <c r="X57" t="str">
-        <v>제품별 상이</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y57" t="str">
-        <v>분진 조건</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z57" t="str">
-        <v>분진 조건</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA57" t="str">
-        <v>분진 폭발 가능, 흡착 포화 시 발열 가능</v>
+        <v>산소결핍 가능, 고온 분해 시 유독가스 생성 가능</v>
       </c>
       <c r="AB57" t="str">
-        <v>슬러리 형태 사용</v>
+        <v>반응성 낮음</v>
       </c>
       <c r="AC57" t="str">
-        <v>흡착 및 회수</v>
+        <v>환기 우선</v>
       </c>
       <c r="AD57" t="str">
-        <v>강산화제</v>
+        <v>고온, 강산화제</v>
       </c>
       <c r="AE57" t="str">
-        <v>회수 및 폐기</v>
+        <v>누출 차단 및 환기</v>
       </c>
       <c r="AF57" t="str">
-        <v>가능</v>
+        <v>확인 필요</v>
       </c>
       <c r="AG57" t="str">
-        <v>가능</v>
+        <v>효과 제한적</v>
       </c>
       <c r="AH57" t="str">
         <v>일반 중화 불필요</v>
       </c>
       <c r="AI57" t="str">
-        <v>방진마스크, 보안경</v>
+        <v>공기호흡기</v>
       </c>
       <c r="AJ57" t="str">
-        <v>건조 분진 주의</v>
+        <v>밀폐공간 질식 위험</v>
       </c>
       <c r="AK57" t="str">
         <v>N</v>
       </c>
       <c r="AL57" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM57" t="str">
         <v>N</v>
@@ -8084,49 +8084,49 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B58" t="str">
-        <v>리튬브로마이드</v>
+        <v>R-134a</v>
       </c>
       <c r="C58" t="str">
-        <v>Lithium Bromide</v>
+        <v>HFC-134a</v>
       </c>
       <c r="D58" t="str">
-        <v>LiBr</v>
+        <v>C2H2F4</v>
       </c>
       <c r="E58" t="str">
-        <v>7550-35-8</v>
+        <v>811-97-2</v>
       </c>
       <c r="F58" t="str">
-        <v>LiBr</v>
+        <v>R134a</v>
       </c>
       <c r="G58" t="str">
-        <v>흡수식 냉동기</v>
+        <v>냉동기 / 공조</v>
       </c>
       <c r="H58" t="str">
-        <v>무색 용액</v>
+        <v>무색 액체 또는 기체</v>
       </c>
       <c r="I58" t="str">
         <v>주의</v>
       </c>
       <c r="J58" t="str">
-        <v>❗ 경고</v>
+        <v>🧯 가스실린더</v>
       </c>
       <c r="K58" t="str">
-        <v>용액: 중성 부근 (흡수식 냉동기 사용)</v>
+        <v>냉매: 해당 없음 (질식 위험 가능)</v>
       </c>
       <c r="L58" t="str">
-        <v>설정 없음</v>
+        <v>1000 ppm</v>
       </c>
       <c r="M58" t="str">
-        <v>-</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N58" t="str">
-        <v>설정 없음</v>
+        <v>1250 ppm</v>
       </c>
       <c r="O58" t="str">
-        <v>-</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="P58" t="str">
         <v>설정 없음</v>
@@ -8141,13 +8141,13 @@
         <v>-</v>
       </c>
       <c r="T58" t="str">
-        <v>1.6 g/cm³</v>
+        <v>1.2 g/cm³</v>
       </c>
       <c r="U58" t="str">
-        <v>낮음</v>
+        <v>높음</v>
       </c>
       <c r="V58" t="str">
-        <v>1265°C</v>
+        <v>-26°C</v>
       </c>
       <c r="W58" t="str">
         <v>비가연성</v>
@@ -8162,40 +8162,40 @@
         <v>해당 없음</v>
       </c>
       <c r="AA58" t="str">
-        <v>흡수식 냉동기 사용, 누출 시 미끄럼 위험</v>
+        <v>산소결핍 가능, 고온 분해 시 HF 생성 가능</v>
       </c>
       <c r="AB58" t="str">
-        <v>수용성</v>
+        <v>반응성 낮음</v>
       </c>
       <c r="AC58" t="str">
-        <v>물 세척 가능</v>
+        <v>환기 우선</v>
       </c>
       <c r="AD58" t="str">
-        <v>강산화제</v>
+        <v>고온, 강산화제</v>
       </c>
       <c r="AE58" t="str">
-        <v>희석 및 회수</v>
+        <v>환기 및 차단</v>
       </c>
       <c r="AF58" t="str">
-        <v>가능</v>
+        <v>확인 필요</v>
       </c>
       <c r="AG58" t="str">
-        <v>가능</v>
+        <v>효과 제한적</v>
       </c>
       <c r="AH58" t="str">
         <v>일반 중화 불필요</v>
       </c>
       <c r="AI58" t="str">
-        <v>보안경, 장갑</v>
+        <v>공기호흡기</v>
       </c>
       <c r="AJ58" t="str">
-        <v>대량 누출 시 미끄럼 위험</v>
+        <v>고온 분해 시 HF 가능</v>
       </c>
       <c r="AK58" t="str">
         <v>N</v>
       </c>
       <c r="AL58" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM58" t="str">
         <v>N</v>
@@ -8207,7 +8207,7 @@
         <v>N</v>
       </c>
       <c r="AP58" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AQ58" t="str">
         <v>N</v>
@@ -8218,28 +8218,28 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B59" t="str">
-        <v>R-123</v>
+        <v>R-410A</v>
       </c>
       <c r="C59" t="str">
-        <v>HCFC-123</v>
+        <v>R-410A</v>
       </c>
       <c r="D59" t="str">
-        <v>C2HCl2F3</v>
+        <v>혼합냉매</v>
       </c>
       <c r="E59" t="str">
-        <v>306-83-2</v>
+        <v>혼합물</v>
       </c>
       <c r="F59" t="str">
-        <v>R123, HCFC-123</v>
+        <v>R410A</v>
       </c>
       <c r="G59" t="str">
-        <v>터보냉동기</v>
+        <v>공조</v>
       </c>
       <c r="H59" t="str">
-        <v>무색 액체</v>
+        <v>무색 액체 또는 기체</v>
       </c>
       <c r="I59" t="str">
         <v>주의</v>
@@ -8248,19 +8248,19 @@
         <v>🧯 가스실린더</v>
       </c>
       <c r="K59" t="str">
-        <v>냉매: 해당 없음 (밀폐공간 질식 위험)</v>
+        <v>냉매: 해당 없음 (질식 위험 가능)</v>
       </c>
       <c r="L59" t="str">
-        <v>50 ppm</v>
+        <v>1000 ppm</v>
       </c>
       <c r="M59" t="str">
         <v>대표 SDS 참고값</v>
       </c>
       <c r="N59" t="str">
-        <v>설정 없음</v>
+        <v>1250 ppm</v>
       </c>
       <c r="O59" t="str">
-        <v>-</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="P59" t="str">
         <v>설정 없음</v>
@@ -8269,19 +8269,19 @@
         <v>-</v>
       </c>
       <c r="R59" t="str">
-        <v>1000 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="S59" t="str">
-        <v>대표 참고값</v>
+        <v>-</v>
       </c>
       <c r="T59" t="str">
-        <v>1.46 g/cm³</v>
+        <v>1.1 g/cm³</v>
       </c>
       <c r="U59" t="str">
-        <v>높음</v>
+        <v>매우 높음</v>
       </c>
       <c r="V59" t="str">
-        <v>27°C</v>
+        <v>-48°C</v>
       </c>
       <c r="W59" t="str">
         <v>비가연성</v>
@@ -8296,7 +8296,7 @@
         <v>해당 없음</v>
       </c>
       <c r="AA59" t="str">
-        <v>산소결핍 가능, 고온 분해 시 유독가스 생성 가능</v>
+        <v>산소결핍 가능, 고압 냉매</v>
       </c>
       <c r="AB59" t="str">
         <v>반응성 낮음</v>
@@ -8305,7 +8305,7 @@
         <v>환기 우선</v>
       </c>
       <c r="AD59" t="str">
-        <v>고온, 강산화제</v>
+        <v>고온</v>
       </c>
       <c r="AE59" t="str">
         <v>누출 차단 및 환기</v>
@@ -8323,7 +8323,7 @@
         <v>공기호흡기</v>
       </c>
       <c r="AJ59" t="str">
-        <v>밀폐공간 질식 위험</v>
+        <v>고압 분출 주의</v>
       </c>
       <c r="AK59" t="str">
         <v>N</v>
@@ -8352,49 +8352,49 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60" t="str">
-        <v>R-134a</v>
+        <v>염화나트륨</v>
       </c>
       <c r="C60" t="str">
-        <v>HFC-134a</v>
+        <v>Sodium Chloride</v>
       </c>
       <c r="D60" t="str">
-        <v>C2H2F4</v>
+        <v>NaCl</v>
       </c>
       <c r="E60" t="str">
-        <v>811-97-2</v>
+        <v>7647-14-5</v>
       </c>
       <c r="F60" t="str">
-        <v>R134a</v>
+        <v>소금, NaCl</v>
       </c>
       <c r="G60" t="str">
-        <v>냉동기 / 공조</v>
+        <v>UPW 재생</v>
       </c>
       <c r="H60" t="str">
-        <v>무색 액체 또는 기체</v>
+        <v>백색 고체</v>
       </c>
       <c r="I60" t="str">
         <v>주의</v>
       </c>
       <c r="J60" t="str">
-        <v>🧯 가스실린더</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K60" t="str">
-        <v>냉매: 해당 없음 (질식 위험 가능)</v>
+        <v>용액: 중성 (재생용 염수)</v>
       </c>
       <c r="L60" t="str">
-        <v>1000 ppm</v>
+        <v>10 mg/m³</v>
       </c>
       <c r="M60" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>분진 기준 참고</v>
       </c>
       <c r="N60" t="str">
-        <v>1250 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="O60" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>-</v>
       </c>
       <c r="P60" t="str">
         <v>설정 없음</v>
@@ -8409,13 +8409,13 @@
         <v>-</v>
       </c>
       <c r="T60" t="str">
-        <v>1.2 g/cm³</v>
+        <v>2.16 g/cm³</v>
       </c>
       <c r="U60" t="str">
-        <v>높음</v>
+        <v>낮음</v>
       </c>
       <c r="V60" t="str">
-        <v>-26°C</v>
+        <v>1413°C</v>
       </c>
       <c r="W60" t="str">
         <v>비가연성</v>
@@ -8430,40 +8430,40 @@
         <v>해당 없음</v>
       </c>
       <c r="AA60" t="str">
-        <v>산소결핍 가능, 고온 분해 시 HF 생성 가능</v>
+        <v>분진 자극 가능</v>
       </c>
       <c r="AB60" t="str">
-        <v>반응성 낮음</v>
+        <v>수용성</v>
       </c>
       <c r="AC60" t="str">
-        <v>환기 우선</v>
+        <v>물 세척 가능</v>
       </c>
       <c r="AD60" t="str">
-        <v>고온, 강산화제</v>
+        <v/>
       </c>
       <c r="AE60" t="str">
-        <v>환기 및 차단</v>
+        <v>일반 세척</v>
       </c>
       <c r="AF60" t="str">
-        <v>확인 필요</v>
+        <v>가능</v>
       </c>
       <c r="AG60" t="str">
-        <v>효과 제한적</v>
+        <v>가능</v>
       </c>
       <c r="AH60" t="str">
-        <v>일반 중화 불필요</v>
+        <v>불필요</v>
       </c>
       <c r="AI60" t="str">
-        <v>공기호흡기</v>
+        <v>보안경</v>
       </c>
       <c r="AJ60" t="str">
-        <v>고온 분해 시 HF 가능</v>
+        <v>바닥 미끄럼 가능</v>
       </c>
       <c r="AK60" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AL60" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM60" t="str">
         <v>N</v>
@@ -8475,7 +8475,7 @@
         <v>N</v>
       </c>
       <c r="AP60" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AQ60" t="str">
         <v>N</v>
@@ -8486,49 +8486,49 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61" t="str">
-        <v>R-410A</v>
+        <v>황산나트륨</v>
       </c>
       <c r="C61" t="str">
-        <v>R-410A</v>
+        <v>Sodium Sulfate</v>
       </c>
       <c r="D61" t="str">
-        <v>혼합냉매</v>
+        <v>Na2SO4</v>
       </c>
       <c r="E61" t="str">
-        <v>혼합물</v>
+        <v>7757-82-6</v>
       </c>
       <c r="F61" t="str">
-        <v>R410A</v>
+        <v>Na2SO4</v>
       </c>
       <c r="G61" t="str">
-        <v>공조</v>
+        <v>수처리 / 재생</v>
       </c>
       <c r="H61" t="str">
-        <v>무색 액체 또는 기체</v>
+        <v>백색 고체</v>
       </c>
       <c r="I61" t="str">
         <v>주의</v>
       </c>
       <c r="J61" t="str">
-        <v>🧯 가스실린더</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K61" t="str">
-        <v>냉매: 해당 없음 (질식 위험 가능)</v>
+        <v>용액: 중성 (수처리용)</v>
       </c>
       <c r="L61" t="str">
-        <v>1000 ppm</v>
+        <v>10 mg/m³</v>
       </c>
       <c r="M61" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>분진 기준 참고</v>
       </c>
       <c r="N61" t="str">
-        <v>1250 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="O61" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>-</v>
       </c>
       <c r="P61" t="str">
         <v>설정 없음</v>
@@ -8543,13 +8543,13 @@
         <v>-</v>
       </c>
       <c r="T61" t="str">
-        <v>1.1 g/cm³</v>
+        <v>2.66 g/cm³</v>
       </c>
       <c r="U61" t="str">
-        <v>매우 높음</v>
+        <v>낮음</v>
       </c>
       <c r="V61" t="str">
-        <v>-48°C</v>
+        <v>분해</v>
       </c>
       <c r="W61" t="str">
         <v>비가연성</v>
@@ -8564,40 +8564,40 @@
         <v>해당 없음</v>
       </c>
       <c r="AA61" t="str">
-        <v>산소결핍 가능, 고압 냉매</v>
+        <v>분진 자극 가능</v>
       </c>
       <c r="AB61" t="str">
-        <v>반응성 낮음</v>
+        <v>수용성</v>
       </c>
       <c r="AC61" t="str">
-        <v>환기 우선</v>
+        <v>물 세척 가능</v>
       </c>
       <c r="AD61" t="str">
-        <v>고온</v>
+        <v/>
       </c>
       <c r="AE61" t="str">
-        <v>누출 차단 및 환기</v>
+        <v>일반 세척</v>
       </c>
       <c r="AF61" t="str">
-        <v>확인 필요</v>
+        <v>가능</v>
       </c>
       <c r="AG61" t="str">
-        <v>효과 제한적</v>
+        <v>가능</v>
       </c>
       <c r="AH61" t="str">
-        <v>일반 중화 불필요</v>
+        <v>불필요</v>
       </c>
       <c r="AI61" t="str">
-        <v>공기호흡기</v>
+        <v>보안경</v>
       </c>
       <c r="AJ61" t="str">
-        <v>고압 분출 주의</v>
+        <v>분진 흡입 주의</v>
       </c>
       <c r="AK61" t="str">
         <v>N</v>
       </c>
       <c r="AL61" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM61" t="str">
         <v>N</v>
@@ -8620,25 +8620,25 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62" t="str">
-        <v>염화나트륨</v>
+        <v>구연산</v>
       </c>
       <c r="C62" t="str">
-        <v>Sodium Chloride</v>
+        <v>Citric Acid</v>
       </c>
       <c r="D62" t="str">
-        <v>NaCl</v>
+        <v>C6H8O7</v>
       </c>
       <c r="E62" t="str">
-        <v>7647-14-5</v>
+        <v>77-92-9</v>
       </c>
       <c r="F62" t="str">
-        <v>소금, NaCl</v>
+        <v>Citric Acid</v>
       </c>
       <c r="G62" t="str">
-        <v>UPW 재생</v>
+        <v>세정 / 수처리</v>
       </c>
       <c r="H62" t="str">
         <v>백색 고체</v>
@@ -8650,7 +8650,7 @@
         <v>❗ 경고</v>
       </c>
       <c r="K62" t="str">
-        <v>용액: 중성 (재생용 염수)</v>
+        <v>용액: 산성 (유기산)</v>
       </c>
       <c r="L62" t="str">
         <v>10 mg/m³</v>
@@ -8677,13 +8677,13 @@
         <v>-</v>
       </c>
       <c r="T62" t="str">
-        <v>2.16 g/cm³</v>
+        <v>1.66 g/cm³</v>
       </c>
       <c r="U62" t="str">
         <v>낮음</v>
       </c>
       <c r="V62" t="str">
-        <v>1413°C</v>
+        <v>분해</v>
       </c>
       <c r="W62" t="str">
         <v>비가연성</v>
@@ -8698,7 +8698,7 @@
         <v>해당 없음</v>
       </c>
       <c r="AA62" t="str">
-        <v>분진 자극 가능</v>
+        <v>눈 자극 가능, 약산성</v>
       </c>
       <c r="AB62" t="str">
         <v>수용성</v>
@@ -8707,10 +8707,10 @@
         <v>물 세척 가능</v>
       </c>
       <c r="AD62" t="str">
-        <v/>
+        <v>강염기</v>
       </c>
       <c r="AE62" t="str">
-        <v>일반 세척</v>
+        <v>알칼리 중화 가능</v>
       </c>
       <c r="AF62" t="str">
         <v>가능</v>
@@ -8719,16 +8719,16 @@
         <v>가능</v>
       </c>
       <c r="AH62" t="str">
-        <v>불필요</v>
+        <v>일반 중화 가능</v>
       </c>
       <c r="AI62" t="str">
-        <v>보안경</v>
+        <v>보안경, 장갑</v>
       </c>
       <c r="AJ62" t="str">
-        <v>바닥 미끄럼 가능</v>
+        <v>분진 흡입 주의</v>
       </c>
       <c r="AK62" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AL62" t="str">
         <v>N</v>
@@ -8754,43 +8754,43 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63" t="str">
-        <v>황산나트륨</v>
+        <v>질산암모늄</v>
       </c>
       <c r="C63" t="str">
-        <v>Sodium Sulfate</v>
+        <v>Ammonium Nitrate</v>
       </c>
       <c r="D63" t="str">
-        <v>Na2SO4</v>
+        <v>NH4NO3</v>
       </c>
       <c r="E63" t="str">
-        <v>7757-82-6</v>
+        <v>6484-52-2</v>
       </c>
       <c r="F63" t="str">
-        <v>Na2SO4</v>
+        <v>질산암모늄</v>
       </c>
       <c r="G63" t="str">
-        <v>수처리 / 재생</v>
+        <v>화학처리 / 산화성</v>
       </c>
       <c r="H63" t="str">
         <v>백색 고체</v>
       </c>
       <c r="I63" t="str">
-        <v>주의</v>
+        <v>고위험</v>
       </c>
       <c r="J63" t="str">
-        <v>❗ 경고</v>
+        <v>⭕ 산화성</v>
       </c>
       <c r="K63" t="str">
-        <v>용액: 중성 (수처리용)</v>
+        <v>용액: 약산성 (산화성)</v>
       </c>
       <c r="L63" t="str">
         <v>10 mg/m³</v>
       </c>
       <c r="M63" t="str">
-        <v>분진 기준 참고</v>
+        <v>대표 참고값</v>
       </c>
       <c r="N63" t="str">
         <v>설정 없음</v>
@@ -8811,7 +8811,7 @@
         <v>-</v>
       </c>
       <c r="T63" t="str">
-        <v>2.66 g/cm³</v>
+        <v>1.72 g/cm³</v>
       </c>
       <c r="U63" t="str">
         <v>낮음</v>
@@ -8820,7 +8820,7 @@
         <v>분해</v>
       </c>
       <c r="W63" t="str">
-        <v>비가연성</v>
+        <v>산화성</v>
       </c>
       <c r="X63" t="str">
         <v>해당 없음</v>
@@ -8832,19 +8832,19 @@
         <v>해당 없음</v>
       </c>
       <c r="AA63" t="str">
-        <v>분진 자극 가능</v>
+        <v>강산화성, 고온 분해 위험</v>
       </c>
       <c r="AB63" t="str">
         <v>수용성</v>
       </c>
       <c r="AC63" t="str">
-        <v>물 세척 가능</v>
+        <v>물 냉각 가능</v>
       </c>
       <c r="AD63" t="str">
-        <v/>
+        <v>유기물, 가연물</v>
       </c>
       <c r="AE63" t="str">
-        <v>일반 세척</v>
+        <v>냉각 및 격리</v>
       </c>
       <c r="AF63" t="str">
         <v>가능</v>
@@ -8853,13 +8853,13 @@
         <v>가능</v>
       </c>
       <c r="AH63" t="str">
-        <v>불필요</v>
+        <v>산화성 관리 우선</v>
       </c>
       <c r="AI63" t="str">
-        <v>보안경</v>
+        <v>보안경, 방진마스크</v>
       </c>
       <c r="AJ63" t="str">
-        <v>분진 흡입 주의</v>
+        <v>가연물 접촉 주의</v>
       </c>
       <c r="AK63" t="str">
         <v>N</v>
@@ -8868,13 +8868,13 @@
         <v>N</v>
       </c>
       <c r="AM63" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN63" t="str">
         <v>Y</v>
       </c>
       <c r="AO63" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP63" t="str">
         <v>N</v>
@@ -8888,97 +8888,97 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B64" t="str">
-        <v>구연산</v>
+        <v>수산화암모늄</v>
       </c>
       <c r="C64" t="str">
-        <v>Citric Acid</v>
+        <v>Ammonium Hydroxide</v>
       </c>
       <c r="D64" t="str">
-        <v>C6H8O7</v>
+        <v>NH4OH</v>
       </c>
       <c r="E64" t="str">
-        <v>77-92-9</v>
+        <v>1336-21-6</v>
       </c>
       <c r="F64" t="str">
-        <v>Citric Acid</v>
+        <v>암모니아수</v>
       </c>
       <c r="G64" t="str">
-        <v>세정 / 수처리</v>
+        <v>세정 / 폐수</v>
       </c>
       <c r="H64" t="str">
-        <v>백색 고체</v>
+        <v>무색 액체</v>
       </c>
       <c r="I64" t="str">
-        <v>주의</v>
+        <v>매우 위험</v>
       </c>
       <c r="J64" t="str">
-        <v>❗ 경고</v>
+        <v>☠️ 급성독성, 🧪 부식성</v>
       </c>
       <c r="K64" t="str">
-        <v>용액: 산성 (유기산)</v>
+        <v>25%: 강염기성 (강한 암모니아 냄새)</v>
       </c>
       <c r="L64" t="str">
-        <v>10 mg/m³</v>
+        <v>25 ppm</v>
       </c>
       <c r="M64" t="str">
-        <v>분진 기준 참고</v>
+        <v>OSHA</v>
       </c>
       <c r="N64" t="str">
-        <v>설정 없음</v>
+        <v>35 ppm</v>
       </c>
       <c r="O64" t="str">
-        <v>-</v>
+        <v>ACGIH</v>
       </c>
       <c r="P64" t="str">
-        <v>설정 없음</v>
+        <v>50 ppm</v>
       </c>
       <c r="Q64" t="str">
-        <v>-</v>
+        <v>NIOSH</v>
       </c>
       <c r="R64" t="str">
-        <v>설정 없음</v>
+        <v>300 ppm</v>
       </c>
       <c r="S64" t="str">
-        <v>-</v>
+        <v>NIOSH</v>
       </c>
       <c r="T64" t="str">
-        <v>1.66 g/cm³</v>
+        <v>0.9 g/cm³</v>
       </c>
       <c r="U64" t="str">
-        <v>낮음</v>
+        <v>높음</v>
       </c>
       <c r="V64" t="str">
-        <v>분해</v>
+        <v>38°C</v>
       </c>
       <c r="W64" t="str">
-        <v>비가연성</v>
+        <v>가연성 가능</v>
       </c>
       <c r="X64" t="str">
-        <v>해당 없음</v>
+        <v>651°C</v>
       </c>
       <c r="Y64" t="str">
-        <v>해당 없음</v>
+        <v>15%</v>
       </c>
       <c r="Z64" t="str">
-        <v>해당 없음</v>
+        <v>28%</v>
       </c>
       <c r="AA64" t="str">
-        <v>눈 자극 가능, 약산성</v>
+        <v>강한 호흡기 자극, 부식성</v>
       </c>
       <c r="AB64" t="str">
         <v>수용성</v>
       </c>
       <c r="AC64" t="str">
-        <v>물 세척 가능</v>
+        <v>대량 물 세척 가능</v>
       </c>
       <c r="AD64" t="str">
-        <v>강염기</v>
+        <v>산, 염소</v>
       </c>
       <c r="AE64" t="str">
-        <v>알칼리 중화 가능</v>
+        <v>산성 중화 검토</v>
       </c>
       <c r="AF64" t="str">
         <v>가능</v>
@@ -8987,19 +8987,19 @@
         <v>가능</v>
       </c>
       <c r="AH64" t="str">
-        <v>일반 중화 가능</v>
+        <v>산 접촉 주의</v>
       </c>
       <c r="AI64" t="str">
-        <v>보안경, 장갑</v>
+        <v>공기호흡기, 내화학 장갑</v>
       </c>
       <c r="AJ64" t="str">
-        <v>분진 흡입 주의</v>
+        <v>고농도 흡입 위험</v>
       </c>
       <c r="AK64" t="str">
         <v>N</v>
       </c>
       <c r="AL64" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM64" t="str">
         <v>N</v>
@@ -9022,49 +9022,49 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B65" t="str">
-        <v>질산암모늄</v>
+        <v>폴리염화비닐 접착제</v>
       </c>
       <c r="C65" t="str">
-        <v>Ammonium Nitrate</v>
+        <v>PVC Cement</v>
       </c>
       <c r="D65" t="str">
-        <v>NH4NO3</v>
+        <v>혼합물</v>
       </c>
       <c r="E65" t="str">
-        <v>6484-52-2</v>
+        <v>혼합물</v>
       </c>
       <c r="F65" t="str">
-        <v>질산암모늄</v>
+        <v>PVC 본드</v>
       </c>
       <c r="G65" t="str">
-        <v>화학처리 / 산화성</v>
+        <v>배관 작업</v>
       </c>
       <c r="H65" t="str">
-        <v>백색 고체</v>
+        <v>무색 액체</v>
       </c>
       <c r="I65" t="str">
         <v>고위험</v>
       </c>
       <c r="J65" t="str">
-        <v>⭕ 산화성</v>
+        <v>🔥 인화성, ❗ 경고</v>
       </c>
       <c r="K65" t="str">
-        <v>용액: 약산성 (산화성)</v>
+        <v>원액: 중성 (유기용제 포함)</v>
       </c>
       <c r="L65" t="str">
-        <v>10 mg/m³</v>
+        <v>THF 기준 적용 가능</v>
       </c>
       <c r="M65" t="str">
-        <v>대표 참고값</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="N65" t="str">
-        <v>설정 없음</v>
+        <v>THF 기준 적용 가능</v>
       </c>
       <c r="O65" t="str">
-        <v>-</v>
+        <v>대표 SDS 참고값</v>
       </c>
       <c r="P65" t="str">
         <v>설정 없음</v>
@@ -9073,61 +9073,61 @@
         <v>-</v>
       </c>
       <c r="R65" t="str">
-        <v>설정 없음</v>
+        <v>제품 SDS 확인</v>
       </c>
       <c r="S65" t="str">
-        <v>-</v>
+        <v>제조사 SDS</v>
       </c>
       <c r="T65" t="str">
-        <v>1.72 g/cm³</v>
+        <v>0.9 g/cm³</v>
       </c>
       <c r="U65" t="str">
-        <v>낮음</v>
+        <v>높음</v>
       </c>
       <c r="V65" t="str">
-        <v>분해</v>
+        <v>혼합물</v>
       </c>
       <c r="W65" t="str">
-        <v>산화성</v>
+        <v>-10°C 이하</v>
       </c>
       <c r="X65" t="str">
-        <v>해당 없음</v>
+        <v>제품별 상이</v>
       </c>
       <c r="Y65" t="str">
-        <v>해당 없음</v>
+        <v>제품별 상이</v>
       </c>
       <c r="Z65" t="str">
-        <v>해당 없음</v>
+        <v>제품별 상이</v>
       </c>
       <c r="AA65" t="str">
-        <v>강산화성, 고온 분해 위험</v>
+        <v>고인화성, 유기용제 증기</v>
       </c>
       <c r="AB65" t="str">
-        <v>수용성</v>
+        <v>물반응성 낮음</v>
       </c>
       <c r="AC65" t="str">
-        <v>물 냉각 가능</v>
+        <v>흡착 및 환기</v>
       </c>
       <c r="AD65" t="str">
-        <v>유기물, 가연물</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE65" t="str">
-        <v>냉각 및 격리</v>
+        <v>흡착 및 회수</v>
       </c>
       <c r="AF65" t="str">
         <v>가능</v>
       </c>
       <c r="AG65" t="str">
-        <v>가능</v>
+        <v>확산 가능성 고려</v>
       </c>
       <c r="AH65" t="str">
-        <v>산화성 관리 우선</v>
+        <v>일반 중화 불필요</v>
       </c>
       <c r="AI65" t="str">
-        <v>보안경, 방진마스크</v>
+        <v>유기증기용 호흡보호구, 방염 보호구</v>
       </c>
       <c r="AJ65" t="str">
-        <v>가연물 접촉 주의</v>
+        <v>밀폐공간 증기 축적 주의</v>
       </c>
       <c r="AK65" t="str">
         <v>N</v>
@@ -9136,13 +9136,13 @@
         <v>N</v>
       </c>
       <c r="AM65" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AN65" t="str">
         <v>Y</v>
       </c>
       <c r="AO65" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AP65" t="str">
         <v>N</v>
@@ -9156,25 +9156,25 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B66" t="str">
-        <v>수산화암모늄</v>
+        <v>테트라하이드로푸란</v>
       </c>
       <c r="C66" t="str">
-        <v>Ammonium Hydroxide</v>
+        <v>Tetrahydrofuran</v>
       </c>
       <c r="D66" t="str">
-        <v>NH4OH</v>
+        <v>C4H8O</v>
       </c>
       <c r="E66" t="str">
-        <v>1336-21-6</v>
+        <v>109-99-9</v>
       </c>
       <c r="F66" t="str">
-        <v>암모니아수</v>
+        <v>THF</v>
       </c>
       <c r="G66" t="str">
-        <v>세정 / 폐수</v>
+        <v>용제 / PVC 작업</v>
       </c>
       <c r="H66" t="str">
         <v>무색 액체</v>
@@ -9183,70 +9183,70 @@
         <v>매우 위험</v>
       </c>
       <c r="J66" t="str">
-        <v>☠️ 급성독성, 🧪 부식성</v>
+        <v>🔥 인화성, ❗ 경고</v>
       </c>
       <c r="K66" t="str">
-        <v>25%: 강염기성 (강한 암모니아 냄새)</v>
+        <v>원액: 중성 (과산화물 생성 가능)</v>
       </c>
       <c r="L66" t="str">
-        <v>25 ppm</v>
+        <v>200 ppm</v>
       </c>
       <c r="M66" t="str">
         <v>OSHA</v>
       </c>
       <c r="N66" t="str">
-        <v>35 ppm</v>
+        <v>250 ppm</v>
       </c>
       <c r="O66" t="str">
         <v>ACGIH</v>
       </c>
       <c r="P66" t="str">
-        <v>50 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q66" t="str">
-        <v>NIOSH</v>
+        <v>-</v>
       </c>
       <c r="R66" t="str">
-        <v>300 ppm</v>
+        <v>2000 ppm</v>
       </c>
       <c r="S66" t="str">
         <v>NIOSH</v>
       </c>
       <c r="T66" t="str">
-        <v>0.9 g/cm³</v>
+        <v>0.89 g/cm³</v>
       </c>
       <c r="U66" t="str">
-        <v>높음</v>
+        <v>143 mmHg</v>
       </c>
       <c r="V66" t="str">
-        <v>38°C</v>
+        <v>66°C</v>
       </c>
       <c r="W66" t="str">
-        <v>가연성 가능</v>
+        <v>-17°C</v>
       </c>
       <c r="X66" t="str">
-        <v>651°C</v>
+        <v>321°C</v>
       </c>
       <c r="Y66" t="str">
-        <v>15%</v>
+        <v>2%</v>
       </c>
       <c r="Z66" t="str">
-        <v>28%</v>
+        <v>12%</v>
       </c>
       <c r="AA66" t="str">
-        <v>강한 호흡기 자극, 부식성</v>
+        <v>고인화성, 과산화물 생성 가능</v>
       </c>
       <c r="AB66" t="str">
-        <v>수용성</v>
+        <v>물 혼합 가능</v>
       </c>
       <c r="AC66" t="str">
-        <v>대량 물 세척 가능</v>
+        <v>흡착 및 환기</v>
       </c>
       <c r="AD66" t="str">
-        <v>산, 염소</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE66" t="str">
-        <v>산성 중화 검토</v>
+        <v>흡착 및 회수</v>
       </c>
       <c r="AF66" t="str">
         <v>가능</v>
@@ -9255,19 +9255,19 @@
         <v>가능</v>
       </c>
       <c r="AH66" t="str">
-        <v>산 접촉 주의</v>
+        <v>일반 중화 불필요</v>
       </c>
       <c r="AI66" t="str">
-        <v>공기호흡기, 내화학 장갑</v>
+        <v>유기증기용 호흡보호구, 방염 보호구</v>
       </c>
       <c r="AJ66" t="str">
-        <v>고농도 흡입 위험</v>
+        <v>장기 보관 시 과산화물 주의</v>
       </c>
       <c r="AK66" t="str">
         <v>N</v>
       </c>
       <c r="AL66" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM66" t="str">
         <v>N</v>
@@ -9290,55 +9290,55 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B67" t="str">
-        <v>폴리염화비닐 접착제</v>
+        <v>과초산</v>
       </c>
       <c r="C67" t="str">
-        <v>PVC Cement</v>
+        <v>Peracetic Acid</v>
       </c>
       <c r="D67" t="str">
-        <v>혼합물</v>
+        <v>C2H4O3</v>
       </c>
       <c r="E67" t="str">
-        <v>혼합물</v>
+        <v>79-21-0</v>
       </c>
       <c r="F67" t="str">
-        <v>PVC 본드</v>
+        <v>PAA, 과초산</v>
       </c>
       <c r="G67" t="str">
-        <v>배관 작업</v>
+        <v>살균 / 폐수</v>
       </c>
       <c r="H67" t="str">
         <v>무색 액체</v>
       </c>
       <c r="I67" t="str">
-        <v>고위험</v>
+        <v>매우 위험</v>
       </c>
       <c r="J67" t="str">
-        <v>🔥 인화성, ❗ 경고</v>
+        <v>⭕ 산화성, 🧪 부식성</v>
       </c>
       <c r="K67" t="str">
-        <v>원액: 중성 (유기용제 포함)</v>
+        <v>15%: 강산성 (강산화성)</v>
       </c>
       <c r="L67" t="str">
-        <v>THF 기준 적용 가능</v>
+        <v>0.4 ppm</v>
       </c>
       <c r="M67" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>ACGIH 참고값</v>
       </c>
       <c r="N67" t="str">
-        <v>THF 기준 적용 가능</v>
+        <v>1 ppm</v>
       </c>
       <c r="O67" t="str">
-        <v>대표 SDS 참고값</v>
+        <v>대표 참고값</v>
       </c>
       <c r="P67" t="str">
-        <v>설정 없음</v>
+        <v>0.4 ppm</v>
       </c>
       <c r="Q67" t="str">
-        <v>-</v>
+        <v>NIOSH 참고</v>
       </c>
       <c r="R67" t="str">
         <v>제품 SDS 확인</v>
@@ -9347,70 +9347,70 @@
         <v>제조사 SDS</v>
       </c>
       <c r="T67" t="str">
-        <v>0.9 g/cm³</v>
+        <v>1.1 g/cm³</v>
       </c>
       <c r="U67" t="str">
-        <v>높음</v>
+        <v>14 mmHg</v>
       </c>
       <c r="V67" t="str">
-        <v>혼합물</v>
+        <v>분해 가능</v>
       </c>
       <c r="W67" t="str">
-        <v>-10°C 이하</v>
+        <v>산화성</v>
       </c>
       <c r="X67" t="str">
-        <v>제품별 상이</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y67" t="str">
-        <v>제품별 상이</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z67" t="str">
-        <v>제품별 상이</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA67" t="str">
-        <v>고인화성, 유기용제 증기</v>
+        <v>강산화성, 유기물 반응 가능, 부식성</v>
       </c>
       <c r="AB67" t="str">
-        <v>물반응성 낮음</v>
+        <v>분해 및 산화 반응 가능</v>
       </c>
       <c r="AC67" t="str">
-        <v>흡착 및 환기</v>
+        <v>희석 및 냉각</v>
       </c>
       <c r="AD67" t="str">
-        <v>산화제, 점화원</v>
+        <v>유기물, 금속, 환원제</v>
       </c>
       <c r="AE67" t="str">
-        <v>흡착 및 회수</v>
+        <v>희석 및 분해 관리</v>
       </c>
       <c r="AF67" t="str">
         <v>가능</v>
       </c>
       <c r="AG67" t="str">
-        <v>확산 가능성 고려</v>
+        <v>가능</v>
       </c>
       <c r="AH67" t="str">
-        <v>일반 중화 불필요</v>
+        <v>산화성 관리 필요</v>
       </c>
       <c r="AI67" t="str">
-        <v>유기증기용 호흡보호구, 방염 보호구</v>
+        <v>공기호흡기, 보안면</v>
       </c>
       <c r="AJ67" t="str">
-        <v>밀폐공간 증기 축적 주의</v>
+        <v>밀폐 시 압력 상승 가능</v>
       </c>
       <c r="AK67" t="str">
         <v>N</v>
       </c>
       <c r="AL67" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM67" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN67" t="str">
         <v>Y</v>
       </c>
       <c r="AO67" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP67" t="str">
         <v>N</v>
@@ -9424,25 +9424,25 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B68" t="str">
-        <v>테트라하이드로푸란</v>
+        <v>포름알데히드</v>
       </c>
       <c r="C68" t="str">
-        <v>Tetrahydrofuran</v>
+        <v>Formaldehyde</v>
       </c>
       <c r="D68" t="str">
-        <v>C4H8O</v>
+        <v>CH2O</v>
       </c>
       <c r="E68" t="str">
-        <v>109-99-9</v>
+        <v>50-00-0</v>
       </c>
       <c r="F68" t="str">
-        <v>THF</v>
+        <v>Formalin, 포르말린</v>
       </c>
       <c r="G68" t="str">
-        <v>용제 / PVC 작업</v>
+        <v>살균 / 분석</v>
       </c>
       <c r="H68" t="str">
         <v>무색 액체</v>
@@ -9451,58 +9451,58 @@
         <v>매우 위험</v>
       </c>
       <c r="J68" t="str">
-        <v>🔥 인화성, ❗ 경고</v>
+        <v>☠️ 급성독성, 🔥 인화성</v>
       </c>
       <c r="K68" t="str">
-        <v>원액: 중성 (과산화물 생성 가능)</v>
+        <v>37%: 약산성 (강한 자극성)</v>
       </c>
       <c r="L68" t="str">
-        <v>200 ppm</v>
+        <v>0.75 ppm</v>
       </c>
       <c r="M68" t="str">
         <v>OSHA</v>
       </c>
       <c r="N68" t="str">
-        <v>250 ppm</v>
+        <v>2 ppm</v>
       </c>
       <c r="O68" t="str">
-        <v>ACGIH</v>
+        <v>OSHA</v>
       </c>
       <c r="P68" t="str">
-        <v>설정 없음</v>
+        <v>2 ppm</v>
       </c>
       <c r="Q68" t="str">
-        <v>-</v>
+        <v>NIOSH 참고</v>
       </c>
       <c r="R68" t="str">
-        <v>2000 ppm</v>
+        <v>20 ppm</v>
       </c>
       <c r="S68" t="str">
         <v>NIOSH</v>
       </c>
       <c r="T68" t="str">
-        <v>0.89 g/cm³</v>
+        <v>1.08 g/cm³</v>
       </c>
       <c r="U68" t="str">
-        <v>143 mmHg</v>
+        <v>높음</v>
       </c>
       <c r="V68" t="str">
-        <v>66°C</v>
+        <v>96°C</v>
       </c>
       <c r="W68" t="str">
-        <v>-17°C</v>
+        <v>50°C</v>
       </c>
       <c r="X68" t="str">
-        <v>321°C</v>
+        <v>300°C</v>
       </c>
       <c r="Y68" t="str">
-        <v>2%</v>
+        <v>7%</v>
       </c>
       <c r="Z68" t="str">
-        <v>12%</v>
+        <v>73%</v>
       </c>
       <c r="AA68" t="str">
-        <v>고인화성, 과산화물 생성 가능</v>
+        <v>발암성 가능, 강한 점막 자극, 인화성</v>
       </c>
       <c r="AB68" t="str">
         <v>물 혼합 가능</v>
@@ -9511,7 +9511,7 @@
         <v>흡착 및 환기</v>
       </c>
       <c r="AD68" t="str">
-        <v>산화제, 점화원</v>
+        <v>산화제, 강염기</v>
       </c>
       <c r="AE68" t="str">
         <v>흡착 및 회수</v>
@@ -9526,16 +9526,16 @@
         <v>일반 중화 불필요</v>
       </c>
       <c r="AI68" t="str">
-        <v>유기증기용 호흡보호구, 방염 보호구</v>
+        <v>공기호흡기, 유기증기용 보호구</v>
       </c>
       <c r="AJ68" t="str">
-        <v>장기 보관 시 과산화물 주의</v>
+        <v>저농도에서도 자극 강함</v>
       </c>
       <c r="AK68" t="str">
         <v>N</v>
       </c>
       <c r="AL68" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM68" t="str">
         <v>N</v>
@@ -9558,97 +9558,97 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B69" t="str">
-        <v>과초산</v>
+        <v>메틸에틸케톤</v>
       </c>
       <c r="C69" t="str">
-        <v>Peracetic Acid</v>
+        <v>Methyl Ethyl Ketone</v>
       </c>
       <c r="D69" t="str">
-        <v>C2H4O3</v>
+        <v>C4H8O</v>
       </c>
       <c r="E69" t="str">
-        <v>79-21-0</v>
+        <v>78-93-3</v>
       </c>
       <c r="F69" t="str">
-        <v>PAA, 과초산</v>
+        <v>MEK</v>
       </c>
       <c r="G69" t="str">
-        <v>살균 / 폐수</v>
+        <v>세정 / 용제</v>
       </c>
       <c r="H69" t="str">
         <v>무색 액체</v>
       </c>
       <c r="I69" t="str">
-        <v>매우 위험</v>
+        <v>고위험</v>
       </c>
       <c r="J69" t="str">
-        <v>⭕ 산화성, 🧪 부식성</v>
+        <v>🔥 인화성</v>
       </c>
       <c r="K69" t="str">
-        <v>15%: 강산성 (강산화성)</v>
+        <v>원액: 중성 (고인화성)</v>
       </c>
       <c r="L69" t="str">
-        <v>0.4 ppm</v>
+        <v>200 ppm</v>
       </c>
       <c r="M69" t="str">
-        <v>ACGIH 참고값</v>
+        <v>OSHA</v>
       </c>
       <c r="N69" t="str">
-        <v>1 ppm</v>
+        <v>300 ppm</v>
       </c>
       <c r="O69" t="str">
-        <v>대표 참고값</v>
+        <v>ACGIH</v>
       </c>
       <c r="P69" t="str">
-        <v>0.4 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q69" t="str">
-        <v>NIOSH 참고</v>
+        <v>-</v>
       </c>
       <c r="R69" t="str">
-        <v>제품 SDS 확인</v>
+        <v>3000 ppm</v>
       </c>
       <c r="S69" t="str">
-        <v>제조사 SDS</v>
+        <v>NIOSH</v>
       </c>
       <c r="T69" t="str">
-        <v>1.1 g/cm³</v>
+        <v>0.8 g/cm³</v>
       </c>
       <c r="U69" t="str">
-        <v>14 mmHg</v>
+        <v>78 mmHg</v>
       </c>
       <c r="V69" t="str">
-        <v>분해 가능</v>
+        <v>80°C</v>
       </c>
       <c r="W69" t="str">
-        <v>산화성</v>
+        <v>-9°C</v>
       </c>
       <c r="X69" t="str">
-        <v>해당 없음</v>
+        <v>404°C</v>
       </c>
       <c r="Y69" t="str">
-        <v>해당 없음</v>
+        <v>1.4%</v>
       </c>
       <c r="Z69" t="str">
-        <v>해당 없음</v>
+        <v>11.4%</v>
       </c>
       <c r="AA69" t="str">
-        <v>강산화성, 유기물 반응 가능, 부식성</v>
+        <v>고인화성, 정전기 점화 가능</v>
       </c>
       <c r="AB69" t="str">
-        <v>분해 및 산화 반응 가능</v>
+        <v>물 혼합 가능</v>
       </c>
       <c r="AC69" t="str">
-        <v>희석 및 냉각</v>
+        <v>흡착 및 환기</v>
       </c>
       <c r="AD69" t="str">
-        <v>유기물, 금속, 환원제</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE69" t="str">
-        <v>희석 및 분해 관리</v>
+        <v>흡착 및 회수</v>
       </c>
       <c r="AF69" t="str">
         <v>가능</v>
@@ -9657,28 +9657,28 @@
         <v>가능</v>
       </c>
       <c r="AH69" t="str">
-        <v>산화성 관리 필요</v>
+        <v>일반 중화 불필요</v>
       </c>
       <c r="AI69" t="str">
-        <v>공기호흡기, 보안면</v>
+        <v>유기증기용 호흡보호구, 방염 보호구</v>
       </c>
       <c r="AJ69" t="str">
-        <v>밀폐 시 압력 상승 가능</v>
+        <v>증기 폭발 위험</v>
       </c>
       <c r="AK69" t="str">
         <v>N</v>
       </c>
       <c r="AL69" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM69" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AN69" t="str">
         <v>Y</v>
       </c>
       <c r="AO69" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AP69" t="str">
         <v>N</v>
@@ -9692,94 +9692,94 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B70" t="str">
-        <v>포름알데히드</v>
+        <v>톨루엔</v>
       </c>
       <c r="C70" t="str">
-        <v>Formaldehyde</v>
+        <v>Toluene</v>
       </c>
       <c r="D70" t="str">
-        <v>CH2O</v>
+        <v>C7H8</v>
       </c>
       <c r="E70" t="str">
-        <v>50-00-0</v>
+        <v>108-88-3</v>
       </c>
       <c r="F70" t="str">
-        <v>Formalin, 포르말린</v>
+        <v>Toluene</v>
       </c>
       <c r="G70" t="str">
-        <v>살균 / 분석</v>
+        <v>세정 / 용제</v>
       </c>
       <c r="H70" t="str">
         <v>무색 액체</v>
       </c>
       <c r="I70" t="str">
-        <v>매우 위험</v>
+        <v>고위험</v>
       </c>
       <c r="J70" t="str">
-        <v>☠️ 급성독성, 🔥 인화성</v>
+        <v>🔥 인화성, ❗ 경고</v>
       </c>
       <c r="K70" t="str">
-        <v>37%: 약산성 (강한 자극성)</v>
+        <v>원액: 중성 (유기용제)</v>
       </c>
       <c r="L70" t="str">
-        <v>0.75 ppm</v>
+        <v>20 ppm</v>
       </c>
       <c r="M70" t="str">
-        <v>OSHA</v>
+        <v>ACGIH</v>
       </c>
       <c r="N70" t="str">
-        <v>2 ppm</v>
+        <v>150 ppm</v>
       </c>
       <c r="O70" t="str">
-        <v>OSHA</v>
+        <v>대표 참고값</v>
       </c>
       <c r="P70" t="str">
-        <v>2 ppm</v>
+        <v>300 ppm</v>
       </c>
       <c r="Q70" t="str">
-        <v>NIOSH 참고</v>
+        <v>OSHA 참고</v>
       </c>
       <c r="R70" t="str">
-        <v>20 ppm</v>
+        <v>500 ppm</v>
       </c>
       <c r="S70" t="str">
         <v>NIOSH</v>
       </c>
       <c r="T70" t="str">
-        <v>1.08 g/cm³</v>
+        <v>0.87 g/cm³</v>
       </c>
       <c r="U70" t="str">
-        <v>높음</v>
+        <v>28 mmHg</v>
       </c>
       <c r="V70" t="str">
-        <v>96°C</v>
+        <v>111°C</v>
       </c>
       <c r="W70" t="str">
-        <v>50°C</v>
+        <v>4°C</v>
       </c>
       <c r="X70" t="str">
-        <v>300°C</v>
+        <v>480°C</v>
       </c>
       <c r="Y70" t="str">
-        <v>7%</v>
+        <v>1.2%</v>
       </c>
       <c r="Z70" t="str">
-        <v>73%</v>
+        <v>7.1%</v>
       </c>
       <c r="AA70" t="str">
-        <v>발암성 가능, 강한 점막 자극, 인화성</v>
+        <v>중추신경계 영향, 고인화성</v>
       </c>
       <c r="AB70" t="str">
-        <v>물 혼합 가능</v>
+        <v>물에 잘 안녹음</v>
       </c>
       <c r="AC70" t="str">
         <v>흡착 및 환기</v>
       </c>
       <c r="AD70" t="str">
-        <v>산화제, 강염기</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE70" t="str">
         <v>흡착 및 회수</v>
@@ -9788,22 +9788,22 @@
         <v>가능</v>
       </c>
       <c r="AG70" t="str">
-        <v>가능</v>
+        <v>확산 가능성 고려</v>
       </c>
       <c r="AH70" t="str">
         <v>일반 중화 불필요</v>
       </c>
       <c r="AI70" t="str">
-        <v>공기호흡기, 유기증기용 보호구</v>
+        <v>유기증기용 호흡보호구, 방염 보호구</v>
       </c>
       <c r="AJ70" t="str">
-        <v>저농도에서도 자극 강함</v>
+        <v>정전기 점화 주의</v>
       </c>
       <c r="AK70" t="str">
         <v>N</v>
       </c>
       <c r="AL70" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM70" t="str">
         <v>N</v>
@@ -9826,49 +9826,49 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B71" t="str">
-        <v>메틸에틸케톤</v>
+        <v>디메틸설폭사이드</v>
       </c>
       <c r="C71" t="str">
-        <v>Methyl Ethyl Ketone</v>
+        <v>Dimethyl Sulfoxide</v>
       </c>
       <c r="D71" t="str">
-        <v>C4H8O</v>
+        <v>C2H6OS</v>
       </c>
       <c r="E71" t="str">
-        <v>78-93-3</v>
+        <v>67-68-5</v>
       </c>
       <c r="F71" t="str">
-        <v>MEK</v>
+        <v>DMSO</v>
       </c>
       <c r="G71" t="str">
-        <v>세정 / 용제</v>
+        <v>세정 / 연구</v>
       </c>
       <c r="H71" t="str">
         <v>무색 액체</v>
       </c>
       <c r="I71" t="str">
-        <v>고위험</v>
+        <v>주의</v>
       </c>
       <c r="J71" t="str">
-        <v>🔥 인화성</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K71" t="str">
-        <v>원액: 중성 (고인화성)</v>
+        <v>원액: 중성 (피부 침투성 높음)</v>
       </c>
       <c r="L71" t="str">
-        <v>200 ppm</v>
+        <v>250 ppm</v>
       </c>
       <c r="M71" t="str">
-        <v>OSHA</v>
+        <v>대표 참고값</v>
       </c>
       <c r="N71" t="str">
-        <v>300 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="O71" t="str">
-        <v>ACGIH</v>
+        <v>-</v>
       </c>
       <c r="P71" t="str">
         <v>설정 없음</v>
@@ -9877,46 +9877,46 @@
         <v>-</v>
       </c>
       <c r="R71" t="str">
-        <v>3000 ppm</v>
+        <v>제품 SDS 확인</v>
       </c>
       <c r="S71" t="str">
-        <v>NIOSH</v>
+        <v>제조사 SDS</v>
       </c>
       <c r="T71" t="str">
-        <v>0.8 g/cm³</v>
+        <v>1.1 g/cm³</v>
       </c>
       <c r="U71" t="str">
-        <v>78 mmHg</v>
+        <v>낮음</v>
       </c>
       <c r="V71" t="str">
-        <v>80°C</v>
+        <v>189°C</v>
       </c>
       <c r="W71" t="str">
-        <v>-9°C</v>
+        <v>89°C</v>
       </c>
       <c r="X71" t="str">
-        <v>404°C</v>
+        <v>215°C</v>
       </c>
       <c r="Y71" t="str">
-        <v>1.4%</v>
+        <v>2.6%</v>
       </c>
       <c r="Z71" t="str">
-        <v>11.4%</v>
+        <v>28%</v>
       </c>
       <c r="AA71" t="str">
-        <v>고인화성, 정전기 점화 가능</v>
+        <v>피부 침투성 높음, 오염물 체내 전달 가능</v>
       </c>
       <c r="AB71" t="str">
         <v>물 혼합 가능</v>
       </c>
       <c r="AC71" t="str">
-        <v>흡착 및 환기</v>
+        <v>물 세척 가능</v>
       </c>
       <c r="AD71" t="str">
-        <v>산화제, 점화원</v>
+        <v>강산화제</v>
       </c>
       <c r="AE71" t="str">
-        <v>흡착 및 회수</v>
+        <v>흡착 및 세척</v>
       </c>
       <c r="AF71" t="str">
         <v>가능</v>
@@ -9928,10 +9928,10 @@
         <v>일반 중화 불필요</v>
       </c>
       <c r="AI71" t="str">
-        <v>유기증기용 호흡보호구, 방염 보호구</v>
+        <v>내화학 장갑, 보안경</v>
       </c>
       <c r="AJ71" t="str">
-        <v>증기 폭발 위험</v>
+        <v>피부 흡수 주의</v>
       </c>
       <c r="AK71" t="str">
         <v>N</v>
@@ -9960,25 +9960,25 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B72" t="str">
-        <v>톨루엔</v>
+        <v>NMP</v>
       </c>
       <c r="C72" t="str">
-        <v>Toluene</v>
+        <v>N-Methyl-2-pyrrolidone</v>
       </c>
       <c r="D72" t="str">
-        <v>C7H8</v>
+        <v>C5H9NO</v>
       </c>
       <c r="E72" t="str">
-        <v>108-88-3</v>
+        <v>872-50-4</v>
       </c>
       <c r="F72" t="str">
-        <v>Toluene</v>
+        <v>NMP</v>
       </c>
       <c r="G72" t="str">
-        <v>세정 / 용제</v>
+        <v>Strip / 세정</v>
       </c>
       <c r="H72" t="str">
         <v>무색 액체</v>
@@ -9987,67 +9987,67 @@
         <v>고위험</v>
       </c>
       <c r="J72" t="str">
-        <v>🔥 인화성, ❗ 경고</v>
+        <v>❗ 경고</v>
       </c>
       <c r="K72" t="str">
-        <v>원액: 중성 (유기용제)</v>
+        <v>원액: 중성 (피부 흡수 가능)</v>
       </c>
       <c r="L72" t="str">
-        <v>20 ppm</v>
+        <v>1 ppm</v>
       </c>
       <c r="M72" t="str">
-        <v>ACGIH</v>
+        <v>ACGIH 참고</v>
       </c>
       <c r="N72" t="str">
-        <v>150 ppm</v>
+        <v>3 ppm</v>
       </c>
       <c r="O72" t="str">
         <v>대표 참고값</v>
       </c>
       <c r="P72" t="str">
-        <v>300 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q72" t="str">
-        <v>OSHA 참고</v>
+        <v>-</v>
       </c>
       <c r="R72" t="str">
-        <v>500 ppm</v>
+        <v>제품 SDS 확인</v>
       </c>
       <c r="S72" t="str">
-        <v>NIOSH</v>
+        <v>제조사 SDS</v>
       </c>
       <c r="T72" t="str">
-        <v>0.87 g/cm³</v>
+        <v>1.03 g/cm³</v>
       </c>
       <c r="U72" t="str">
-        <v>28 mmHg</v>
+        <v>낮음</v>
       </c>
       <c r="V72" t="str">
-        <v>111°C</v>
+        <v>202°C</v>
       </c>
       <c r="W72" t="str">
-        <v>4°C</v>
+        <v>91°C</v>
       </c>
       <c r="X72" t="str">
-        <v>480°C</v>
+        <v>270°C</v>
       </c>
       <c r="Y72" t="str">
-        <v>1.2%</v>
+        <v>1.3%</v>
       </c>
       <c r="Z72" t="str">
-        <v>7.1%</v>
+        <v>9.5%</v>
       </c>
       <c r="AA72" t="str">
-        <v>중추신경계 영향, 고인화성</v>
+        <v>피부 흡수 가능, 생식독성 우려</v>
       </c>
       <c r="AB72" t="str">
-        <v>물에 잘 안녹음</v>
+        <v>물 혼합 가능</v>
       </c>
       <c r="AC72" t="str">
-        <v>흡착 및 환기</v>
+        <v>흡착 및 세척</v>
       </c>
       <c r="AD72" t="str">
-        <v>산화제, 점화원</v>
+        <v>강산화제</v>
       </c>
       <c r="AE72" t="str">
         <v>흡착 및 회수</v>
@@ -10056,16 +10056,16 @@
         <v>가능</v>
       </c>
       <c r="AG72" t="str">
-        <v>확산 가능성 고려</v>
+        <v>가능</v>
       </c>
       <c r="AH72" t="str">
         <v>일반 중화 불필요</v>
       </c>
       <c r="AI72" t="str">
-        <v>유기증기용 호흡보호구, 방염 보호구</v>
+        <v>내화학 장갑, 유기증기용 보호구</v>
       </c>
       <c r="AJ72" t="str">
-        <v>정전기 점화 주의</v>
+        <v>피부 노출 최소화</v>
       </c>
       <c r="AK72" t="str">
         <v>N</v>
@@ -10094,49 +10094,49 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B73" t="str">
-        <v>디메틸설폭사이드</v>
+        <v>디메틸아세트아마이드</v>
       </c>
       <c r="C73" t="str">
-        <v>Dimethyl Sulfoxide</v>
+        <v>Dimethylacetamide</v>
       </c>
       <c r="D73" t="str">
-        <v>C2H6OS</v>
+        <v>C4H9NO</v>
       </c>
       <c r="E73" t="str">
-        <v>67-68-5</v>
+        <v>127-19-5</v>
       </c>
       <c r="F73" t="str">
-        <v>DMSO</v>
+        <v>DMAc</v>
       </c>
       <c r="G73" t="str">
-        <v>세정 / 연구</v>
+        <v>세정 / 용제</v>
       </c>
       <c r="H73" t="str">
         <v>무색 액체</v>
       </c>
       <c r="I73" t="str">
-        <v>주의</v>
+        <v>고위험</v>
       </c>
       <c r="J73" t="str">
         <v>❗ 경고</v>
       </c>
       <c r="K73" t="str">
-        <v>원액: 중성 (피부 침투성 높음)</v>
+        <v>원액: 중성 (피부 흡수 가능)</v>
       </c>
       <c r="L73" t="str">
-        <v>250 ppm</v>
+        <v>10 ppm</v>
       </c>
       <c r="M73" t="str">
+        <v>OSHA 참고</v>
+      </c>
+      <c r="N73" t="str">
+        <v>20 ppm</v>
+      </c>
+      <c r="O73" t="str">
         <v>대표 참고값</v>
-      </c>
-      <c r="N73" t="str">
-        <v>설정 없음</v>
-      </c>
-      <c r="O73" t="str">
-        <v>-</v>
       </c>
       <c r="P73" t="str">
         <v>설정 없음</v>
@@ -10145,46 +10145,46 @@
         <v>-</v>
       </c>
       <c r="R73" t="str">
-        <v>제품 SDS 확인</v>
+        <v>300 ppm</v>
       </c>
       <c r="S73" t="str">
-        <v>제조사 SDS</v>
+        <v>대표 참고값</v>
       </c>
       <c r="T73" t="str">
-        <v>1.1 g/cm³</v>
+        <v>0.94 g/cm³</v>
       </c>
       <c r="U73" t="str">
-        <v>낮음</v>
+        <v>2 mmHg</v>
       </c>
       <c r="V73" t="str">
-        <v>189°C</v>
+        <v>166°C</v>
       </c>
       <c r="W73" t="str">
-        <v>89°C</v>
+        <v>63°C</v>
       </c>
       <c r="X73" t="str">
-        <v>215°C</v>
+        <v>345°C</v>
       </c>
       <c r="Y73" t="str">
-        <v>2.6%</v>
+        <v>1.8%</v>
       </c>
       <c r="Z73" t="str">
-        <v>28%</v>
+        <v>11.5%</v>
       </c>
       <c r="AA73" t="str">
-        <v>피부 침투성 높음, 오염물 체내 전달 가능</v>
+        <v>피부 흡수 가능, 간 독성 가능</v>
       </c>
       <c r="AB73" t="str">
         <v>물 혼합 가능</v>
       </c>
       <c r="AC73" t="str">
-        <v>물 세척 가능</v>
+        <v>흡착 및 세척</v>
       </c>
       <c r="AD73" t="str">
         <v>강산화제</v>
       </c>
       <c r="AE73" t="str">
-        <v>흡착 및 세척</v>
+        <v>흡착 및 회수</v>
       </c>
       <c r="AF73" t="str">
         <v>가능</v>
@@ -10196,7 +10196,7 @@
         <v>일반 중화 불필요</v>
       </c>
       <c r="AI73" t="str">
-        <v>내화학 장갑, 보안경</v>
+        <v>내화학 장갑, 유기증기용 보호구</v>
       </c>
       <c r="AJ73" t="str">
         <v>피부 흡수 주의</v>
@@ -10228,25 +10228,25 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B74" t="str">
-        <v>NMP</v>
+        <v>디메틸포름아마이드</v>
       </c>
       <c r="C74" t="str">
-        <v>N-Methyl-2-pyrrolidone</v>
+        <v>Dimethylformamide</v>
       </c>
       <c r="D74" t="str">
-        <v>C5H9NO</v>
+        <v>C3H7NO</v>
       </c>
       <c r="E74" t="str">
-        <v>872-50-4</v>
+        <v>68-12-2</v>
       </c>
       <c r="F74" t="str">
-        <v>NMP</v>
+        <v>DMF</v>
       </c>
       <c r="G74" t="str">
-        <v>Strip / 세정</v>
+        <v>세정 / 용제</v>
       </c>
       <c r="H74" t="str">
         <v>무색 액체</v>
@@ -10255,19 +10255,19 @@
         <v>고위험</v>
       </c>
       <c r="J74" t="str">
-        <v>❗ 경고</v>
+        <v>❗ 경고, 🔥 인화성</v>
       </c>
       <c r="K74" t="str">
         <v>원액: 중성 (피부 흡수 가능)</v>
       </c>
       <c r="L74" t="str">
-        <v>1 ppm</v>
+        <v>10 ppm</v>
       </c>
       <c r="M74" t="str">
-        <v>ACGIH 참고</v>
+        <v>OSHA</v>
       </c>
       <c r="N74" t="str">
-        <v>3 ppm</v>
+        <v>15 ppm</v>
       </c>
       <c r="O74" t="str">
         <v>대표 참고값</v>
@@ -10279,34 +10279,34 @@
         <v>-</v>
       </c>
       <c r="R74" t="str">
-        <v>제품 SDS 확인</v>
+        <v>500 ppm</v>
       </c>
       <c r="S74" t="str">
-        <v>제조사 SDS</v>
+        <v>대표 참고값</v>
       </c>
       <c r="T74" t="str">
-        <v>1.03 g/cm³</v>
+        <v>0.94 g/cm³</v>
       </c>
       <c r="U74" t="str">
-        <v>낮음</v>
+        <v>3 mmHg</v>
       </c>
       <c r="V74" t="str">
-        <v>202°C</v>
+        <v>153°C</v>
       </c>
       <c r="W74" t="str">
-        <v>91°C</v>
+        <v>58°C</v>
       </c>
       <c r="X74" t="str">
-        <v>270°C</v>
+        <v>445°C</v>
       </c>
       <c r="Y74" t="str">
-        <v>1.3%</v>
+        <v>2.2%</v>
       </c>
       <c r="Z74" t="str">
-        <v>9.5%</v>
+        <v>15%</v>
       </c>
       <c r="AA74" t="str">
-        <v>피부 흡수 가능, 생식독성 우려</v>
+        <v>피부 흡수 가능, 간 독성 가능, 인화성</v>
       </c>
       <c r="AB74" t="str">
         <v>물 혼합 가능</v>
@@ -10362,46 +10362,46 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75" t="str">
-        <v>디메틸아세트아마이드</v>
+        <v>과염소산</v>
       </c>
       <c r="C75" t="str">
-        <v>Dimethylacetamide</v>
+        <v>Perchloric Acid</v>
       </c>
       <c r="D75" t="str">
-        <v>C4H9NO</v>
+        <v>HClO4</v>
       </c>
       <c r="E75" t="str">
-        <v>127-19-5</v>
+        <v>7601-90-3</v>
       </c>
       <c r="F75" t="str">
-        <v>DMAc</v>
+        <v>과염소산</v>
       </c>
       <c r="G75" t="str">
-        <v>세정 / 용제</v>
+        <v>분석 / 세정</v>
       </c>
       <c r="H75" t="str">
         <v>무색 액체</v>
       </c>
       <c r="I75" t="str">
-        <v>고위험</v>
+        <v>매우 위험</v>
       </c>
       <c r="J75" t="str">
-        <v>❗ 경고</v>
+        <v>⭕ 산화성, 🧪 부식성</v>
       </c>
       <c r="K75" t="str">
-        <v>원액: 중성 (피부 흡수 가능)</v>
+        <v>70%: 강산성 (폭발성 산화제 가능)</v>
       </c>
       <c r="L75" t="str">
-        <v>10 ppm</v>
+        <v>1 mg/m³</v>
       </c>
       <c r="M75" t="str">
         <v>OSHA 참고</v>
       </c>
       <c r="N75" t="str">
-        <v>20 ppm</v>
+        <v>3 mg/m³</v>
       </c>
       <c r="O75" t="str">
         <v>대표 참고값</v>
@@ -10413,76 +10413,76 @@
         <v>-</v>
       </c>
       <c r="R75" t="str">
-        <v>300 ppm</v>
+        <v>150 mg/m³</v>
       </c>
       <c r="S75" t="str">
         <v>대표 참고값</v>
       </c>
       <c r="T75" t="str">
-        <v>0.94 g/cm³</v>
+        <v>1.76 g/cm³</v>
       </c>
       <c r="U75" t="str">
-        <v>2 mmHg</v>
+        <v>낮음</v>
       </c>
       <c r="V75" t="str">
-        <v>166°C</v>
+        <v>203°C</v>
       </c>
       <c r="W75" t="str">
-        <v>63°C</v>
+        <v>산화성</v>
       </c>
       <c r="X75" t="str">
-        <v>345°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y75" t="str">
-        <v>1.8%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z75" t="str">
-        <v>11.5%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA75" t="str">
-        <v>피부 흡수 가능, 간 독성 가능</v>
+        <v>폭발성 산화제 가능, 강부식성</v>
       </c>
       <c r="AB75" t="str">
-        <v>물 혼합 가능</v>
+        <v>유기물과 격렬 반응 가능</v>
       </c>
       <c r="AC75" t="str">
-        <v>흡착 및 세척</v>
+        <v>냉각 및 희석</v>
       </c>
       <c r="AD75" t="str">
-        <v>강산화제</v>
+        <v>유기물, 환원제, 금속</v>
       </c>
       <c r="AE75" t="str">
-        <v>흡착 및 회수</v>
+        <v>냉각 및 격리 우선</v>
       </c>
       <c r="AF75" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AG75" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AH75" t="str">
-        <v>일반 중화 불필요</v>
+        <v>산화성 관리 필요</v>
       </c>
       <c r="AI75" t="str">
-        <v>내화학 장갑, 유기증기용 보호구</v>
+        <v>공기호흡기, 보안면</v>
       </c>
       <c r="AJ75" t="str">
-        <v>피부 흡수 주의</v>
+        <v>유기물 접촉 절대 주의</v>
       </c>
       <c r="AK75" t="str">
         <v>N</v>
       </c>
       <c r="AL75" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM75" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN75" t="str">
         <v>Y</v>
       </c>
       <c r="AO75" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP75" t="str">
         <v>N</v>
@@ -10496,46 +10496,46 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76" t="str">
-        <v>디메틸포름아마이드</v>
+        <v>과산화벤조일</v>
       </c>
       <c r="C76" t="str">
-        <v>Dimethylformamide</v>
+        <v>Benzoyl Peroxide</v>
       </c>
       <c r="D76" t="str">
-        <v>C3H7NO</v>
+        <v>C14H10O4</v>
       </c>
       <c r="E76" t="str">
-        <v>68-12-2</v>
+        <v>94-36-0</v>
       </c>
       <c r="F76" t="str">
-        <v>DMF</v>
+        <v>BPO</v>
       </c>
       <c r="G76" t="str">
-        <v>세정 / 용제</v>
+        <v>화학공정 / 개시제</v>
       </c>
       <c r="H76" t="str">
-        <v>무색 액체</v>
+        <v>백색 고체</v>
       </c>
       <c r="I76" t="str">
-        <v>고위험</v>
+        <v>매우 위험</v>
       </c>
       <c r="J76" t="str">
-        <v>❗ 경고, 🔥 인화성</v>
+        <v>⭕ 산화성, 🔥 폭발성</v>
       </c>
       <c r="K76" t="str">
-        <v>원액: 중성 (피부 흡수 가능)</v>
+        <v>고체: 해당 없음 (열분해 위험)</v>
       </c>
       <c r="L76" t="str">
-        <v>10 ppm</v>
+        <v>5 mg/m³</v>
       </c>
       <c r="M76" t="str">
-        <v>OSHA</v>
+        <v>OSHA 참고</v>
       </c>
       <c r="N76" t="str">
-        <v>15 ppm</v>
+        <v>10 mg/m³</v>
       </c>
       <c r="O76" t="str">
         <v>대표 참고값</v>
@@ -10547,61 +10547,61 @@
         <v>-</v>
       </c>
       <c r="R76" t="str">
-        <v>500 ppm</v>
+        <v>700 mg/m³</v>
       </c>
       <c r="S76" t="str">
         <v>대표 참고값</v>
       </c>
       <c r="T76" t="str">
-        <v>0.94 g/cm³</v>
+        <v>1.3 g/cm³</v>
       </c>
       <c r="U76" t="str">
-        <v>3 mmHg</v>
+        <v>낮음</v>
       </c>
       <c r="V76" t="str">
-        <v>153°C</v>
+        <v>분해</v>
       </c>
       <c r="W76" t="str">
-        <v>58°C</v>
+        <v>폭발성</v>
       </c>
       <c r="X76" t="str">
-        <v>445°C</v>
+        <v>80°C 이상 분해 가능</v>
       </c>
       <c r="Y76" t="str">
-        <v>2.2%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z76" t="str">
-        <v>15%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA76" t="str">
-        <v>피부 흡수 가능, 간 독성 가능, 인화성</v>
+        <v>열분해 위험, 산화성, 폭발 가능</v>
       </c>
       <c r="AB76" t="str">
-        <v>물 혼합 가능</v>
+        <v>열·충격 민감</v>
       </c>
       <c r="AC76" t="str">
-        <v>흡착 및 세척</v>
+        <v>냉각 및 격리</v>
       </c>
       <c r="AD76" t="str">
-        <v>강산화제</v>
+        <v>환원제, 유기물, 금속분말</v>
       </c>
       <c r="AE76" t="str">
-        <v>흡착 및 회수</v>
+        <v>냉각 및 격리 우선</v>
       </c>
       <c r="AF76" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AG76" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AH76" t="str">
-        <v>일반 중화 불필요</v>
+        <v>산화성 관리 필요</v>
       </c>
       <c r="AI76" t="str">
-        <v>내화학 장갑, 유기증기용 보호구</v>
+        <v>보안면, 방염 보호구</v>
       </c>
       <c r="AJ76" t="str">
-        <v>피부 노출 최소화</v>
+        <v>충격 및 마찰 주의</v>
       </c>
       <c r="AK76" t="str">
         <v>N</v>
@@ -10610,13 +10610,13 @@
         <v>N</v>
       </c>
       <c r="AM76" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN76" t="str">
         <v>Y</v>
       </c>
       <c r="AO76" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP76" t="str">
         <v>N</v>
@@ -10630,25 +10630,25 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B77" t="str">
-        <v>과염소산</v>
+        <v>메탄올</v>
       </c>
       <c r="C77" t="str">
-        <v>Perchloric Acid</v>
+        <v>Methanol</v>
       </c>
       <c r="D77" t="str">
-        <v>HClO4</v>
+        <v>CH4O</v>
       </c>
       <c r="E77" t="str">
-        <v>7601-90-3</v>
+        <v>67-56-1</v>
       </c>
       <c r="F77" t="str">
-        <v>과염소산</v>
+        <v>MeOH</v>
       </c>
       <c r="G77" t="str">
-        <v>분석 / 세정</v>
+        <v>세정 / 용제</v>
       </c>
       <c r="H77" t="str">
         <v>무색 액체</v>
@@ -10657,85 +10657,85 @@
         <v>매우 위험</v>
       </c>
       <c r="J77" t="str">
-        <v>⭕ 산화성, 🧪 부식성</v>
+        <v>🔥 인화성, ☠️ 급성독성</v>
       </c>
       <c r="K77" t="str">
-        <v>70%: 강산성 (폭발성 산화제 가능)</v>
+        <v>원액: 중성 (독성 알코올)</v>
       </c>
       <c r="L77" t="str">
-        <v>1 mg/m³</v>
+        <v>200 ppm</v>
       </c>
       <c r="M77" t="str">
-        <v>OSHA 참고</v>
+        <v>OSHA</v>
       </c>
       <c r="N77" t="str">
-        <v>3 mg/m³</v>
+        <v>250 ppm</v>
       </c>
       <c r="O77" t="str">
-        <v>대표 참고값</v>
+        <v>ACGIH</v>
       </c>
       <c r="P77" t="str">
-        <v>설정 없음</v>
+        <v>250 ppm</v>
       </c>
       <c r="Q77" t="str">
-        <v>-</v>
+        <v>NIOSH 참고</v>
       </c>
       <c r="R77" t="str">
-        <v>150 mg/m³</v>
+        <v>6000 ppm</v>
       </c>
       <c r="S77" t="str">
-        <v>대표 참고값</v>
+        <v>NIOSH</v>
       </c>
       <c r="T77" t="str">
-        <v>1.76 g/cm³</v>
+        <v>0.79 g/cm³</v>
       </c>
       <c r="U77" t="str">
-        <v>낮음</v>
+        <v>97 mmHg</v>
       </c>
       <c r="V77" t="str">
-        <v>203°C</v>
+        <v>65°C</v>
       </c>
       <c r="W77" t="str">
-        <v>산화성</v>
+        <v>11°C</v>
       </c>
       <c r="X77" t="str">
-        <v>해당 없음</v>
+        <v>464°C</v>
       </c>
       <c r="Y77" t="str">
-        <v>해당 없음</v>
+        <v>6%</v>
       </c>
       <c r="Z77" t="str">
-        <v>해당 없음</v>
+        <v>36%</v>
       </c>
       <c r="AA77" t="str">
-        <v>폭발성 산화제 가능, 강부식성</v>
+        <v>시신경 독성, 고인화성</v>
       </c>
       <c r="AB77" t="str">
-        <v>유기물과 격렬 반응 가능</v>
+        <v>물 혼합 가능</v>
       </c>
       <c r="AC77" t="str">
-        <v>냉각 및 희석</v>
+        <v>흡착 및 환기</v>
       </c>
       <c r="AD77" t="str">
-        <v>유기물, 환원제, 금속</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE77" t="str">
-        <v>냉각 및 격리 우선</v>
+        <v>흡착 및 회수</v>
       </c>
       <c r="AF77" t="str">
-        <v>주의</v>
+        <v>가능</v>
       </c>
       <c r="AG77" t="str">
-        <v>주의</v>
+        <v>가능</v>
       </c>
       <c r="AH77" t="str">
-        <v>산화성 관리 필요</v>
+        <v>불필요</v>
       </c>
       <c r="AI77" t="str">
-        <v>공기호흡기, 보안면</v>
+        <v>공기호흡기, 유기증기용 보호구</v>
       </c>
       <c r="AJ77" t="str">
-        <v>유기물 접촉 절대 주의</v>
+        <v>섭취 및 흡입 독성 위험</v>
       </c>
       <c r="AK77" t="str">
         <v>N</v>
@@ -10744,13 +10744,13 @@
         <v>Y</v>
       </c>
       <c r="AM77" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AN77" t="str">
         <v>Y</v>
       </c>
       <c r="AO77" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AP77" t="str">
         <v>N</v>
@@ -10764,112 +10764,112 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B78" t="str">
-        <v>과산화벤조일</v>
+        <v>아세톤</v>
       </c>
       <c r="C78" t="str">
-        <v>Benzoyl Peroxide</v>
+        <v>Acetone</v>
       </c>
       <c r="D78" t="str">
-        <v>C14H10O4</v>
+        <v>C3H6O</v>
       </c>
       <c r="E78" t="str">
-        <v>94-36-0</v>
+        <v>67-64-1</v>
       </c>
       <c r="F78" t="str">
-        <v>BPO</v>
+        <v>Acetone</v>
       </c>
       <c r="G78" t="str">
-        <v>화학공정 / 개시제</v>
+        <v>세정 / 용제</v>
       </c>
       <c r="H78" t="str">
-        <v>백색 고체</v>
+        <v>무색 액체</v>
       </c>
       <c r="I78" t="str">
-        <v>매우 위험</v>
+        <v>고위험</v>
       </c>
       <c r="J78" t="str">
-        <v>⭕ 산화성, 🔥 폭발성</v>
+        <v>🔥 인화성</v>
       </c>
       <c r="K78" t="str">
-        <v>고체: 해당 없음 (열분해 위험)</v>
+        <v>원액: 중성 (휘발성 용제)</v>
       </c>
       <c r="L78" t="str">
-        <v>5 mg/m³</v>
+        <v>250 ppm</v>
       </c>
       <c r="M78" t="str">
-        <v>OSHA 참고</v>
+        <v>OSHA</v>
       </c>
       <c r="N78" t="str">
-        <v>10 mg/m³</v>
+        <v>500 ppm</v>
       </c>
       <c r="O78" t="str">
-        <v>대표 참고값</v>
+        <v>ACGIH</v>
       </c>
       <c r="P78" t="str">
-        <v>설정 없음</v>
+        <v>1000 ppm</v>
       </c>
       <c r="Q78" t="str">
-        <v>-</v>
+        <v>NIOSH 참고</v>
       </c>
       <c r="R78" t="str">
-        <v>700 mg/m³</v>
+        <v>2500 ppm</v>
       </c>
       <c r="S78" t="str">
-        <v>대표 참고값</v>
+        <v>NIOSH</v>
       </c>
       <c r="T78" t="str">
-        <v>1.3 g/cm³</v>
+        <v>0.79 g/cm³</v>
       </c>
       <c r="U78" t="str">
-        <v>낮음</v>
+        <v>180 mmHg</v>
       </c>
       <c r="V78" t="str">
-        <v>분해</v>
+        <v>56°C</v>
       </c>
       <c r="W78" t="str">
-        <v>폭발성</v>
+        <v>-20°C</v>
       </c>
       <c r="X78" t="str">
-        <v>80°C 이상 분해 가능</v>
+        <v>465°C</v>
       </c>
       <c r="Y78" t="str">
-        <v>해당 없음</v>
+        <v>2.6%</v>
       </c>
       <c r="Z78" t="str">
-        <v>해당 없음</v>
+        <v>12.8%</v>
       </c>
       <c r="AA78" t="str">
-        <v>열분해 위험, 산화성, 폭발 가능</v>
+        <v>고인화성, 정전기 점화 가능</v>
       </c>
       <c r="AB78" t="str">
-        <v>열·충격 민감</v>
+        <v>물 혼합 가능</v>
       </c>
       <c r="AC78" t="str">
-        <v>냉각 및 격리</v>
+        <v>흡착 및 환기</v>
       </c>
       <c r="AD78" t="str">
-        <v>환원제, 유기물, 금속분말</v>
+        <v>산화제, 점화원</v>
       </c>
       <c r="AE78" t="str">
-        <v>냉각 및 격리 우선</v>
+        <v>흡착 및 회수</v>
       </c>
       <c r="AF78" t="str">
-        <v>주의</v>
+        <v>가능</v>
       </c>
       <c r="AG78" t="str">
-        <v>주의</v>
+        <v>가능</v>
       </c>
       <c r="AH78" t="str">
-        <v>산화성 관리 필요</v>
+        <v>불필요</v>
       </c>
       <c r="AI78" t="str">
-        <v>보안면, 방염 보호구</v>
+        <v>유기증기용 보호구, 방염 보호구</v>
       </c>
       <c r="AJ78" t="str">
-        <v>충격 및 마찰 주의</v>
+        <v>증기 폭발 위험</v>
       </c>
       <c r="AK78" t="str">
         <v>N</v>
@@ -10878,13 +10878,13 @@
         <v>N</v>
       </c>
       <c r="AM78" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AN78" t="str">
         <v>Y</v>
       </c>
       <c r="AO78" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AP78" t="str">
         <v>N</v>
@@ -10898,118 +10898,118 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B79" t="str">
-        <v>에틸렌글리콜</v>
+        <v>브롬</v>
       </c>
       <c r="C79" t="str">
-        <v>Ethylene Glycol</v>
+        <v>Bromine</v>
       </c>
       <c r="D79" t="str">
-        <v>C2H6O2</v>
+        <v>Br2</v>
       </c>
       <c r="E79" t="str">
-        <v>107-21-1</v>
+        <v>7726-95-6</v>
       </c>
       <c r="F79" t="str">
-        <v>EG, 부동액</v>
+        <v>Br2</v>
       </c>
       <c r="G79" t="str">
-        <v>공조 / 냉각수</v>
+        <v>화학처리</v>
       </c>
       <c r="H79" t="str">
-        <v>무색 액체</v>
+        <v>적갈색 액체</v>
       </c>
       <c r="I79" t="str">
-        <v>주의</v>
+        <v>매우 위험</v>
       </c>
       <c r="J79" t="str">
-        <v>❗ 경고</v>
+        <v>☠️ 급성독성, 🧪 부식성</v>
       </c>
       <c r="K79" t="str">
-        <v>원액: 중성 (부동액)</v>
+        <v>용액: 산성 (강한 자극성)</v>
       </c>
       <c r="L79" t="str">
-        <v>50 ppm</v>
+        <v>0.1 ppm</v>
       </c>
       <c r="M79" t="str">
-        <v>ACGIH 참고</v>
+        <v>OSHA</v>
       </c>
       <c r="N79" t="str">
-        <v>100 ppm</v>
+        <v>0.3 ppm</v>
       </c>
       <c r="O79" t="str">
-        <v>대표 참고값</v>
+        <v>ACGIH</v>
       </c>
       <c r="P79" t="str">
-        <v>100 mg/m³</v>
+        <v>0.3 ppm</v>
       </c>
       <c r="Q79" t="str">
         <v>NIOSH 참고</v>
       </c>
       <c r="R79" t="str">
-        <v>설정 없음</v>
+        <v>3 ppm</v>
       </c>
       <c r="S79" t="str">
-        <v>-</v>
+        <v>NIOSH</v>
       </c>
       <c r="T79" t="str">
-        <v>1.11 g/cm³</v>
+        <v>3.1 g/cm³</v>
       </c>
       <c r="U79" t="str">
-        <v>낮음</v>
+        <v>높음</v>
       </c>
       <c r="V79" t="str">
-        <v>197°C</v>
+        <v>59°C</v>
       </c>
       <c r="W79" t="str">
-        <v>111°C</v>
+        <v>비가연성</v>
       </c>
       <c r="X79" t="str">
-        <v>410°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y79" t="str">
-        <v>3.2%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z79" t="str">
-        <v>15%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA79" t="str">
-        <v>섭취 독성, 미끄럼 위험</v>
+        <v>강한 부식성, 고독성 증기, 저지대 체류 가능</v>
       </c>
       <c r="AB79" t="str">
-        <v>물 혼합 가능</v>
+        <v>물과 반응 가능</v>
       </c>
       <c r="AC79" t="str">
-        <v>물 세척 가능</v>
+        <v>환기 및 희석</v>
       </c>
       <c r="AD79" t="str">
-        <v>강산화제</v>
+        <v>금속, 환원제</v>
       </c>
       <c r="AE79" t="str">
-        <v>흡착 및 회수</v>
+        <v>격리 및 흡수</v>
       </c>
       <c r="AF79" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AG79" t="str">
-        <v>가능</v>
+        <v>주의</v>
       </c>
       <c r="AH79" t="str">
-        <v>불필요</v>
+        <v>전용 처리 검토</v>
       </c>
       <c r="AI79" t="str">
-        <v>보안경, 장갑</v>
+        <v>공기호흡기, 보안면</v>
       </c>
       <c r="AJ79" t="str">
-        <v>바닥 미끄럼 주의</v>
+        <v>증기 흡입 위험</v>
       </c>
       <c r="AK79" t="str">
         <v>Y</v>
       </c>
       <c r="AL79" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AM79" t="str">
         <v>N</v>
@@ -11032,43 +11032,43 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B80" t="str">
-        <v>프로필렌글리콜</v>
+        <v>질산은</v>
       </c>
       <c r="C80" t="str">
-        <v>Propylene Glycol</v>
+        <v>Silver Nitrate</v>
       </c>
       <c r="D80" t="str">
-        <v>C3H8O2</v>
+        <v>AgNO3</v>
       </c>
       <c r="E80" t="str">
-        <v>57-55-6</v>
+        <v>7761-88-8</v>
       </c>
       <c r="F80" t="str">
-        <v>PG</v>
+        <v>AgNO3</v>
       </c>
       <c r="G80" t="str">
-        <v>공조 / 부동액</v>
+        <v>분석 / 화학처리</v>
       </c>
       <c r="H80" t="str">
-        <v>무색 액체</v>
+        <v>무색 고체</v>
       </c>
       <c r="I80" t="str">
-        <v>주의</v>
+        <v>고위험</v>
       </c>
       <c r="J80" t="str">
-        <v>❗ 경고</v>
+        <v>⭕ 산화성, 🧪 부식성</v>
       </c>
       <c r="K80" t="str">
-        <v>원액: 중성 (저독성 부동액)</v>
+        <v>용액: 산성 (산화성)</v>
       </c>
       <c r="L80" t="str">
-        <v>10 mg/m³</v>
+        <v>0.01 mg/m³</v>
       </c>
       <c r="M80" t="str">
-        <v>대표 참고값</v>
+        <v>OSHA 참고</v>
       </c>
       <c r="N80" t="str">
         <v>설정 없음</v>
@@ -11077,52 +11077,52 @@
         <v>-</v>
       </c>
       <c r="P80" t="str">
-        <v>155 mg/m³</v>
+        <v>0.03 mg/m³</v>
       </c>
       <c r="Q80" t="str">
         <v>대표 참고값</v>
       </c>
       <c r="R80" t="str">
-        <v>설정 없음</v>
+        <v>10 mg/m³</v>
       </c>
       <c r="S80" t="str">
-        <v>-</v>
+        <v>대표 참고값</v>
       </c>
       <c r="T80" t="str">
-        <v>1.03 g/cm³</v>
+        <v>4.35 g/cm³</v>
       </c>
       <c r="U80" t="str">
         <v>낮음</v>
       </c>
       <c r="V80" t="str">
-        <v>188°C</v>
+        <v>분해</v>
       </c>
       <c r="W80" t="str">
-        <v>99°C</v>
+        <v>산화성</v>
       </c>
       <c r="X80" t="str">
-        <v>371°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y80" t="str">
-        <v>2.6%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z80" t="str">
-        <v>12.5%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA80" t="str">
-        <v>미끄럼 위험</v>
+        <v>산화성, 피부 착색</v>
       </c>
       <c r="AB80" t="str">
-        <v>물 혼합 가능</v>
+        <v>수용성</v>
       </c>
       <c r="AC80" t="str">
-        <v>물 세척 가능</v>
+        <v>회수 및 세척</v>
       </c>
       <c r="AD80" t="str">
-        <v>강산화제</v>
+        <v>환원제, 유기물</v>
       </c>
       <c r="AE80" t="str">
-        <v>흡착 및 회수</v>
+        <v>격리 및 회수</v>
       </c>
       <c r="AF80" t="str">
         <v>가능</v>
@@ -11131,13 +11131,13 @@
         <v>가능</v>
       </c>
       <c r="AH80" t="str">
-        <v>불필요</v>
+        <v>산화성 관리</v>
       </c>
       <c r="AI80" t="str">
-        <v>보안경</v>
+        <v>보안면, 장갑</v>
       </c>
       <c r="AJ80" t="str">
-        <v>누출 시 미끄럼 주의</v>
+        <v>빛 반응성 주의</v>
       </c>
       <c r="AK80" t="str">
         <v>N</v>
@@ -11146,13 +11146,13 @@
         <v>N</v>
       </c>
       <c r="AM80" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN80" t="str">
         <v>Y</v>
       </c>
       <c r="AO80" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP80" t="str">
         <v>N</v>
@@ -11166,97 +11166,97 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B81" t="str">
-        <v>메탄올</v>
+        <v>질산구리</v>
       </c>
       <c r="C81" t="str">
-        <v>Methanol</v>
+        <v>Copper Nitrate</v>
       </c>
       <c r="D81" t="str">
-        <v>CH4O</v>
+        <v>Cu(NO3)2</v>
       </c>
       <c r="E81" t="str">
-        <v>67-56-1</v>
+        <v>3251-23-8</v>
       </c>
       <c r="F81" t="str">
-        <v>MeOH</v>
+        <v>CuNitrate</v>
       </c>
       <c r="G81" t="str">
-        <v>세정 / 용제</v>
+        <v>폐수 / 화학처리</v>
       </c>
       <c r="H81" t="str">
-        <v>무색 액체</v>
+        <v>청색 고체</v>
       </c>
       <c r="I81" t="str">
-        <v>매우 위험</v>
+        <v>고위험</v>
       </c>
       <c r="J81" t="str">
-        <v>🔥 인화성, ☠️ 급성독성</v>
+        <v>⭕ 산화성, ❗ 경고</v>
       </c>
       <c r="K81" t="str">
-        <v>원액: 중성 (독성 알코올)</v>
+        <v>용액: 산성 (산화성)</v>
       </c>
       <c r="L81" t="str">
-        <v>200 ppm</v>
+        <v>1 mg/m³</v>
       </c>
       <c r="M81" t="str">
-        <v>OSHA</v>
+        <v>구리 기준 참고</v>
       </c>
       <c r="N81" t="str">
-        <v>250 ppm</v>
+        <v>2 mg/m³</v>
       </c>
       <c r="O81" t="str">
-        <v>ACGIH</v>
+        <v>대표 참고값</v>
       </c>
       <c r="P81" t="str">
-        <v>250 ppm</v>
+        <v>설정 없음</v>
       </c>
       <c r="Q81" t="str">
-        <v>NIOSH 참고</v>
+        <v>-</v>
       </c>
       <c r="R81" t="str">
-        <v>6000 ppm</v>
+        <v>100 mg/m³</v>
       </c>
       <c r="S81" t="str">
-        <v>NIOSH</v>
+        <v>대표 참고값</v>
       </c>
       <c r="T81" t="str">
-        <v>0.79 g/cm³</v>
+        <v>2.3 g/cm³</v>
       </c>
       <c r="U81" t="str">
-        <v>97 mmHg</v>
+        <v>낮음</v>
       </c>
       <c r="V81" t="str">
-        <v>65°C</v>
+        <v>분해</v>
       </c>
       <c r="W81" t="str">
-        <v>11°C</v>
+        <v>산화성</v>
       </c>
       <c r="X81" t="str">
-        <v>464°C</v>
+        <v>해당 없음</v>
       </c>
       <c r="Y81" t="str">
-        <v>6%</v>
+        <v>해당 없음</v>
       </c>
       <c r="Z81" t="str">
-        <v>36%</v>
+        <v>해당 없음</v>
       </c>
       <c r="AA81" t="str">
-        <v>시신경 독성, 고인화성</v>
+        <v>산화성, 중금속 위험</v>
       </c>
       <c r="AB81" t="str">
-        <v>물 혼합 가능</v>
+        <v>수용성</v>
       </c>
       <c r="AC81" t="str">
-        <v>흡착 및 환기</v>
+        <v>회수 및 세척</v>
       </c>
       <c r="AD81" t="str">
-        <v>산화제, 점화원</v>
+        <v>환원제, 유기물</v>
       </c>
       <c r="AE81" t="str">
-        <v>흡착 및 회수</v>
+        <v>회수 및 격리</v>
       </c>
       <c r="AF81" t="str">
         <v>가능</v>
@@ -11265,28 +11265,28 @@
         <v>가능</v>
       </c>
       <c r="AH81" t="str">
-        <v>불필요</v>
+        <v>중금속 처리 필요</v>
       </c>
       <c r="AI81" t="str">
-        <v>공기호흡기, 유기증기용 보호구</v>
+        <v>보안경, 장갑</v>
       </c>
       <c r="AJ81" t="str">
-        <v>섭취 및 흡입 독성 위험</v>
+        <v>중금속 폐기 기준 준수</v>
       </c>
       <c r="AK81" t="str">
         <v>N</v>
       </c>
       <c r="AL81" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="AM81" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AN81" t="str">
         <v>Y</v>
       </c>
       <c r="AO81" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="AP81" t="str">
         <v>N</v>
@@ -11295,548 +11295,12 @@
         <v>N</v>
       </c>
       <c r="AR81" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="str">
-        <v>아세톤</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Acetone</v>
-      </c>
-      <c r="D82" t="str">
-        <v>C3H6O</v>
-      </c>
-      <c r="E82" t="str">
-        <v>67-64-1</v>
-      </c>
-      <c r="F82" t="str">
-        <v>Acetone</v>
-      </c>
-      <c r="G82" t="str">
-        <v>세정 / 용제</v>
-      </c>
-      <c r="H82" t="str">
-        <v>무색 액체</v>
-      </c>
-      <c r="I82" t="str">
-        <v>고위험</v>
-      </c>
-      <c r="J82" t="str">
-        <v>🔥 인화성</v>
-      </c>
-      <c r="K82" t="str">
-        <v>원액: 중성 (휘발성 용제)</v>
-      </c>
-      <c r="L82" t="str">
-        <v>250 ppm</v>
-      </c>
-      <c r="M82" t="str">
-        <v>OSHA</v>
-      </c>
-      <c r="N82" t="str">
-        <v>500 ppm</v>
-      </c>
-      <c r="O82" t="str">
-        <v>ACGIH</v>
-      </c>
-      <c r="P82" t="str">
-        <v>1000 ppm</v>
-      </c>
-      <c r="Q82" t="str">
-        <v>NIOSH 참고</v>
-      </c>
-      <c r="R82" t="str">
-        <v>2500 ppm</v>
-      </c>
-      <c r="S82" t="str">
-        <v>NIOSH</v>
-      </c>
-      <c r="T82" t="str">
-        <v>0.79 g/cm³</v>
-      </c>
-      <c r="U82" t="str">
-        <v>180 mmHg</v>
-      </c>
-      <c r="V82" t="str">
-        <v>56°C</v>
-      </c>
-      <c r="W82" t="str">
-        <v>-20°C</v>
-      </c>
-      <c r="X82" t="str">
-        <v>465°C</v>
-      </c>
-      <c r="Y82" t="str">
-        <v>2.6%</v>
-      </c>
-      <c r="Z82" t="str">
-        <v>12.8%</v>
-      </c>
-      <c r="AA82" t="str">
-        <v>고인화성, 정전기 점화 가능</v>
-      </c>
-      <c r="AB82" t="str">
-        <v>물 혼합 가능</v>
-      </c>
-      <c r="AC82" t="str">
-        <v>흡착 및 환기</v>
-      </c>
-      <c r="AD82" t="str">
-        <v>산화제, 점화원</v>
-      </c>
-      <c r="AE82" t="str">
-        <v>흡착 및 회수</v>
-      </c>
-      <c r="AF82" t="str">
-        <v>가능</v>
-      </c>
-      <c r="AG82" t="str">
-        <v>가능</v>
-      </c>
-      <c r="AH82" t="str">
-        <v>불필요</v>
-      </c>
-      <c r="AI82" t="str">
-        <v>유기증기용 보호구, 방염 보호구</v>
-      </c>
-      <c r="AJ82" t="str">
-        <v>증기 폭발 위험</v>
-      </c>
-      <c r="AK82" t="str">
-        <v>N</v>
-      </c>
-      <c r="AL82" t="str">
-        <v>N</v>
-      </c>
-      <c r="AM82" t="str">
-        <v>N</v>
-      </c>
-      <c r="AN82" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AO82" t="str">
-        <v>N</v>
-      </c>
-      <c r="AP82" t="str">
-        <v>N</v>
-      </c>
-      <c r="AQ82" t="str">
-        <v>N</v>
-      </c>
-      <c r="AR82" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="str">
-        <v>브롬</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Bromine</v>
-      </c>
-      <c r="D83" t="str">
-        <v>Br2</v>
-      </c>
-      <c r="E83" t="str">
-        <v>7726-95-6</v>
-      </c>
-      <c r="F83" t="str">
-        <v>Br2</v>
-      </c>
-      <c r="G83" t="str">
-        <v>화학처리</v>
-      </c>
-      <c r="H83" t="str">
-        <v>적갈색 액체</v>
-      </c>
-      <c r="I83" t="str">
-        <v>매우 위험</v>
-      </c>
-      <c r="J83" t="str">
-        <v>☠️ 급성독성, 🧪 부식성</v>
-      </c>
-      <c r="K83" t="str">
-        <v>용액: 산성 (강한 자극성)</v>
-      </c>
-      <c r="L83" t="str">
-        <v>0.1 ppm</v>
-      </c>
-      <c r="M83" t="str">
-        <v>OSHA</v>
-      </c>
-      <c r="N83" t="str">
-        <v>0.3 ppm</v>
-      </c>
-      <c r="O83" t="str">
-        <v>ACGIH</v>
-      </c>
-      <c r="P83" t="str">
-        <v>0.3 ppm</v>
-      </c>
-      <c r="Q83" t="str">
-        <v>NIOSH 참고</v>
-      </c>
-      <c r="R83" t="str">
-        <v>3 ppm</v>
-      </c>
-      <c r="S83" t="str">
-        <v>NIOSH</v>
-      </c>
-      <c r="T83" t="str">
-        <v>3.1 g/cm³</v>
-      </c>
-      <c r="U83" t="str">
-        <v>높음</v>
-      </c>
-      <c r="V83" t="str">
-        <v>59°C</v>
-      </c>
-      <c r="W83" t="str">
-        <v>비가연성</v>
-      </c>
-      <c r="X83" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="Y83" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="Z83" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="AA83" t="str">
-        <v>강한 부식성, 고독성 증기, 저지대 체류 가능</v>
-      </c>
-      <c r="AB83" t="str">
-        <v>물과 반응 가능</v>
-      </c>
-      <c r="AC83" t="str">
-        <v>환기 및 희석</v>
-      </c>
-      <c r="AD83" t="str">
-        <v>금속, 환원제</v>
-      </c>
-      <c r="AE83" t="str">
-        <v>격리 및 흡수</v>
-      </c>
-      <c r="AF83" t="str">
-        <v>주의</v>
-      </c>
-      <c r="AG83" t="str">
-        <v>주의</v>
-      </c>
-      <c r="AH83" t="str">
-        <v>전용 처리 검토</v>
-      </c>
-      <c r="AI83" t="str">
-        <v>공기호흡기, 보안면</v>
-      </c>
-      <c r="AJ83" t="str">
-        <v>증기 흡입 위험</v>
-      </c>
-      <c r="AK83" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AL83" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AM83" t="str">
-        <v>N</v>
-      </c>
-      <c r="AN83" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AO83" t="str">
-        <v>N</v>
-      </c>
-      <c r="AP83" t="str">
-        <v>N</v>
-      </c>
-      <c r="AQ83" t="str">
-        <v>N</v>
-      </c>
-      <c r="AR83" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="str">
-        <v>질산은</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Silver Nitrate</v>
-      </c>
-      <c r="D84" t="str">
-        <v>AgNO3</v>
-      </c>
-      <c r="E84" t="str">
-        <v>7761-88-8</v>
-      </c>
-      <c r="F84" t="str">
-        <v>AgNO3</v>
-      </c>
-      <c r="G84" t="str">
-        <v>분석 / 화학처리</v>
-      </c>
-      <c r="H84" t="str">
-        <v>무색 고체</v>
-      </c>
-      <c r="I84" t="str">
-        <v>고위험</v>
-      </c>
-      <c r="J84" t="str">
-        <v>⭕ 산화성, 🧪 부식성</v>
-      </c>
-      <c r="K84" t="str">
-        <v>용액: 산성 (산화성)</v>
-      </c>
-      <c r="L84" t="str">
-        <v>0.01 mg/m³</v>
-      </c>
-      <c r="M84" t="str">
-        <v>OSHA 참고</v>
-      </c>
-      <c r="N84" t="str">
-        <v>설정 없음</v>
-      </c>
-      <c r="O84" t="str">
-        <v>-</v>
-      </c>
-      <c r="P84" t="str">
-        <v>0.03 mg/m³</v>
-      </c>
-      <c r="Q84" t="str">
-        <v>대표 참고값</v>
-      </c>
-      <c r="R84" t="str">
-        <v>10 mg/m³</v>
-      </c>
-      <c r="S84" t="str">
-        <v>대표 참고값</v>
-      </c>
-      <c r="T84" t="str">
-        <v>4.35 g/cm³</v>
-      </c>
-      <c r="U84" t="str">
-        <v>낮음</v>
-      </c>
-      <c r="V84" t="str">
-        <v>분해</v>
-      </c>
-      <c r="W84" t="str">
-        <v>산화성</v>
-      </c>
-      <c r="X84" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="Y84" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="Z84" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="AA84" t="str">
-        <v>산화성, 피부 착색</v>
-      </c>
-      <c r="AB84" t="str">
-        <v>수용성</v>
-      </c>
-      <c r="AC84" t="str">
-        <v>회수 및 세척</v>
-      </c>
-      <c r="AD84" t="str">
-        <v>환원제, 유기물</v>
-      </c>
-      <c r="AE84" t="str">
-        <v>격리 및 회수</v>
-      </c>
-      <c r="AF84" t="str">
-        <v>가능</v>
-      </c>
-      <c r="AG84" t="str">
-        <v>가능</v>
-      </c>
-      <c r="AH84" t="str">
-        <v>산화성 관리</v>
-      </c>
-      <c r="AI84" t="str">
-        <v>보안면, 장갑</v>
-      </c>
-      <c r="AJ84" t="str">
-        <v>빛 반응성 주의</v>
-      </c>
-      <c r="AK84" t="str">
-        <v>N</v>
-      </c>
-      <c r="AL84" t="str">
-        <v>N</v>
-      </c>
-      <c r="AM84" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AN84" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AO84" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AP84" t="str">
-        <v>N</v>
-      </c>
-      <c r="AQ84" t="str">
-        <v>N</v>
-      </c>
-      <c r="AR84" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
-        <v>질산구리</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Copper Nitrate</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Cu(NO3)2</v>
-      </c>
-      <c r="E85" t="str">
-        <v>3251-23-8</v>
-      </c>
-      <c r="F85" t="str">
-        <v>CuNitrate</v>
-      </c>
-      <c r="G85" t="str">
-        <v>폐수 / 화학처리</v>
-      </c>
-      <c r="H85" t="str">
-        <v>청색 고체</v>
-      </c>
-      <c r="I85" t="str">
-        <v>고위험</v>
-      </c>
-      <c r="J85" t="str">
-        <v>⭕ 산화성, ❗ 경고</v>
-      </c>
-      <c r="K85" t="str">
-        <v>용액: 산성 (산화성)</v>
-      </c>
-      <c r="L85" t="str">
-        <v>1 mg/m³</v>
-      </c>
-      <c r="M85" t="str">
-        <v>구리 기준 참고</v>
-      </c>
-      <c r="N85" t="str">
-        <v>2 mg/m³</v>
-      </c>
-      <c r="O85" t="str">
-        <v>대표 참고값</v>
-      </c>
-      <c r="P85" t="str">
-        <v>설정 없음</v>
-      </c>
-      <c r="Q85" t="str">
-        <v>-</v>
-      </c>
-      <c r="R85" t="str">
-        <v>100 mg/m³</v>
-      </c>
-      <c r="S85" t="str">
-        <v>대표 참고값</v>
-      </c>
-      <c r="T85" t="str">
-        <v>2.3 g/cm³</v>
-      </c>
-      <c r="U85" t="str">
-        <v>낮음</v>
-      </c>
-      <c r="V85" t="str">
-        <v>분해</v>
-      </c>
-      <c r="W85" t="str">
-        <v>산화성</v>
-      </c>
-      <c r="X85" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="Y85" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="Z85" t="str">
-        <v>해당 없음</v>
-      </c>
-      <c r="AA85" t="str">
-        <v>산화성, 중금속 위험</v>
-      </c>
-      <c r="AB85" t="str">
-        <v>수용성</v>
-      </c>
-      <c r="AC85" t="str">
-        <v>회수 및 세척</v>
-      </c>
-      <c r="AD85" t="str">
-        <v>환원제, 유기물</v>
-      </c>
-      <c r="AE85" t="str">
-        <v>회수 및 격리</v>
-      </c>
-      <c r="AF85" t="str">
-        <v>가능</v>
-      </c>
-      <c r="AG85" t="str">
-        <v>가능</v>
-      </c>
-      <c r="AH85" t="str">
-        <v>중금속 처리 필요</v>
-      </c>
-      <c r="AI85" t="str">
-        <v>보안경, 장갑</v>
-      </c>
-      <c r="AJ85" t="str">
-        <v>중금속 폐기 기준 준수</v>
-      </c>
-      <c r="AK85" t="str">
-        <v>N</v>
-      </c>
-      <c r="AL85" t="str">
-        <v>N</v>
-      </c>
-      <c r="AM85" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AN85" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AO85" t="str">
-        <v>Y</v>
-      </c>
-      <c r="AP85" t="str">
-        <v>N</v>
-      </c>
-      <c r="AQ85" t="str">
-        <v>N</v>
-      </c>
-      <c r="AR85" t="str">
         <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AR85"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AR81"/>
   </ignoredErrors>
 </worksheet>
 </file>